--- a/Results/Phase 2/Carbon dioxide/carbon dioxide climate change results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide climate change results.xlsx
@@ -2265,10 +2265,10 @@
         <v>-0.2476859044812906</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2597225537143494</v>
+        <v>-0.2597225537143495</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4188207911471424</v>
+        <v>-0.4188207911471425</v>
       </c>
       <c r="M4" t="n">
         <v>-0.2690560356240144</v>
@@ -2987,7 +2987,7 @@
         <v>-0.369258201457435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.3384635920809559</v>
+        <v>-0.338463592080956</v>
       </c>
       <c r="R12" t="n">
         <v>-0.6971961296631879</v>
@@ -3033,10 +3033,10 @@
         <v>-0.3399358500670698</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="E13" t="n">
         <v>-0.3381935434607085</v>
@@ -3048,19 +3048,19 @@
         <v>-0.3354364864127439</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="J13" t="n">
         <v>-0.3435253013553399</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="M13" t="n">
         <v>-0.3362092261571308</v>
@@ -3078,13 +3078,13 @@
         <v>-0.3406682167214815</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="U13" t="n">
         <v>-0.33806020406265</v>
@@ -3105,7 +3105,7 @@
         <v>-0.3400050740195011</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.3362092261571426</v>
+        <v>-0.3362092261571427</v>
       </c>
       <c r="AB13" t="n">
         <v>-0.3323164558678551</v>
@@ -5014,13 +5014,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5336208512089557</v>
+        <v>-0.5336208512089589</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7665467488295029</v>
+        <v>-0.766546748829503</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.362979350566775</v>
+        <v>-0.3629793505667782</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7334313477294088</v>
@@ -5029,70 +5029,70 @@
         <v>-0.7244567052039743</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1642585529027923</v>
+        <v>-0.1642585529027948</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5266143997303151</v>
+        <v>-0.5266143997303169</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6519246825604101</v>
+        <v>-0.651924682560413</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3557125138375585</v>
+        <v>-0.3557125138375639</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.526006358607348</v>
+        <v>-0.5260063586073507</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.24795084401078</v>
+        <v>-0.2479508440107844</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1029466351301661</v>
+        <v>-0.1029466351301667</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5240775476558386</v>
+        <v>-0.5240775476558399</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5650647672919397</v>
+        <v>-0.5650647672919408</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3508690246508873</v>
+        <v>-0.3508690246508871</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7487093677080454</v>
+        <v>-0.7487093677080476</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5987342255670803</v>
+        <v>-0.5987342255670822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3190388266863602</v>
+        <v>-0.3190388266863616</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5712330229440157</v>
+        <v>-0.5712330229440188</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3551411722559459</v>
+        <v>-0.3551411722559495</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6532305775493895</v>
+        <v>-0.6532305775493897</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2580182959148158</v>
+        <v>-0.2580182959148177</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2335750523268173</v>
+        <v>-0.2335750523268206</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.3187622036572429</v>
+        <v>-0.3187622036572436</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5289924440608753</v>
+        <v>-0.5289924440608786</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4204802467523017</v>
+        <v>-0.4204802467523051</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.04592818741886211</v>
+        <v>-0.04592818741886267</v>
       </c>
     </row>
     <row r="3">
@@ -5102,82 +5102,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9317917972346147</v>
+        <v>-0.9317917972346174</v>
       </c>
       <c r="C3" t="n">
         <v>-0.9216078188049571</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9286389715561262</v>
+        <v>-0.9286389715561261</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9314640981373977</v>
+        <v>-0.9314640981373976</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9182227958299509</v>
+        <v>-0.91822279582995</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9214126686060667</v>
+        <v>-0.9214126686060682</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="M3" t="n">
         <v>-0.920398320324438</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9292649915784406</v>
+        <v>-0.9292649915784418</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.926870913832635</v>
+        <v>-0.9268709138326351</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9274577601368135</v>
+        <v>-0.9274577601368124</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9340004393710298</v>
+        <v>-0.9340004393710331</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9260455065458029</v>
+        <v>-0.9260455065458043</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9257689959910974</v>
+        <v>-0.9257689959910979</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9205509848208976</v>
+        <v>-0.9205509848208998</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9329703990133507</v>
+        <v>-0.9329703990133527</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9093907104888398</v>
+        <v>-0.9093907104888403</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9320005600679461</v>
+        <v>-0.9320005600679466</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9205531935219662</v>
+        <v>-0.9205531935219655</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.9075486336525801</v>
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04261465181096259</v>
+        <v>-0.04261465181097067</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1281836330910426</v>
+        <v>-0.1281836330910485</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01958217139944456</v>
+        <v>0.01958217139943415</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.116778793157187</v>
+        <v>-0.116778793157189</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1130765044154911</v>
+        <v>-0.1130765044154988</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09201356865054795</v>
+        <v>0.09201356865053788</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04006088252090782</v>
+        <v>-0.04006088252091363</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08573500914484253</v>
+        <v>-0.08573500914485201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008645600938046462</v>
+        <v>0.008645600938035881</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03983925867156377</v>
+        <v>-0.03983925867157095</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06150871130619076</v>
+        <v>0.0615087113061768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1144594664534136</v>
+        <v>0.1144594664534004</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03913622972898113</v>
+        <v>-0.03913622972898888</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05407558999010693</v>
+        <v>-0.05407558999011286</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02399624298915951</v>
+        <v>0.02399624298914908</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1210118903780013</v>
+        <v>-0.1210118903780128</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.06634771216465457</v>
+        <v>-0.06634771216466487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03559797637817474</v>
+        <v>0.03559797637816143</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05632384674397168</v>
+        <v>-0.05632384674398361</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02243909535320983</v>
+        <v>0.02243909535320143</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1745618640657851</v>
+        <v>-0.174561864065784</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05783924330515192</v>
+        <v>0.0578392433051428</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06674851856592065</v>
+        <v>0.06674851856591618</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03569880222401673</v>
+        <v>0.0356988022240078</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.04092765175498837</v>
+        <v>-0.040927651755</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.001376230050566178</v>
+        <v>-0.001376230050576611</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1359474552400204</v>
+        <v>0.1359474552400045</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1877432860780169</v>
+        <v>-0.1877432860780209</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1847015722780827</v>
+        <v>-0.1847015722780912</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1879296797983754</v>
+        <v>-0.1879296797983746</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1885282683361814</v>
+        <v>-0.1885282683361995</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1827975444012686</v>
+        <v>-0.1827975444012736</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1975454626884878</v>
+        <v>-0.1975454626884904</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1834920737975762</v>
+        <v>-0.1834920737975878</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1868222950875789</v>
+        <v>-0.1868222950875915</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1859496818619132</v>
+        <v>-0.1859496818619241</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1861635804486906</v>
+        <v>-0.1861635804487022</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1885483102015471</v>
+        <v>-0.1885483102015588</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1856488305982913</v>
+        <v>-0.185648830598291</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2738989172801002</v>
+        <v>-0.2738989172800967</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1836461419494895</v>
+        <v>-0.183646141949503</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1881728725865153</v>
+        <v>-0.1881728725865275</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1795783530060171</v>
+        <v>-0.179578353006025</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1878193776793318</v>
+        <v>-0.1878193776793493</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1836469469950935</v>
+        <v>-0.1836469469951043</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1781030797540827</v>
+        <v>-0.1781030797540833</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7609804010450644</v>
+        <v>-0.7609804010450655</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8465493823251488</v>
+        <v>-0.8465493823251486</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6987835778346564</v>
+        <v>-0.6987835778346569</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8351445423912831</v>
+        <v>-0.835144542391283</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8314422536495949</v>
+        <v>-0.8314422536495948</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6632757272479453</v>
+        <v>-0.6632757272479484</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7584266317550067</v>
+        <v>-0.7584266317550081</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8041007583789439</v>
+        <v>-0.8041007583789459</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.732036272589361</v>
+        <v>-0.7320362725893625</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7582050079056644</v>
+        <v>-0.7582050079056658</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6568570379279143</v>
+        <v>-0.6568570379279167</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6039062827806907</v>
+        <v>-0.6039062827806909</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7575019789630814</v>
+        <v>-0.757501978963082</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8093648858886004</v>
+        <v>-0.8093648858886018</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.731293052909334</v>
+        <v>-0.7312930529093354</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8393776396121044</v>
+        <v>-0.8393776396121059</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7847134613987558</v>
+        <v>-0.7847134613987571</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6827677728559264</v>
+        <v>-0.6827677728559279</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7746895959780744</v>
+        <v>-0.7746895959780754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7328502005452887</v>
+        <v>-0.7328502005452904</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8403548177319257</v>
+        <v>-0.8403548177319252</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6974500525933408</v>
+        <v>-0.6974500525933424</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6885407773325729</v>
+        <v>-0.6885407773325742</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.682666947010084</v>
+        <v>-0.6826669470100861</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7592934009890895</v>
+        <v>-0.7592934009890915</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7197419792846678</v>
+        <v>-0.719741979284669</v>
       </c>
       <c r="AB6" t="n">
         <v>-0.5824182939940883</v>
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9061090353121095</v>
+        <v>-0.9061090353121114</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9030673215121886</v>
+        <v>-0.9030673215121885</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="E7" t="n">
         <v>-0.906295429032472</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9068940175702939</v>
+        <v>-0.9068940175702938</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9380868402997632</v>
+        <v>-0.9380868402997617</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9382273362158837</v>
+        <v>-0.9382273362158864</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="M7" t="n">
         <v>-0.901857823031683</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9051880443216836</v>
+        <v>-0.9051880443216865</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9412389777604104</v>
+        <v>-0.9412389777604119</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9414528763471854</v>
+        <v>-0.9414528763471876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9069140594356498</v>
+        <v>-0.9069140594356492</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.940938126496784</v>
+        <v>-0.9409381264967837</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9396918709462421</v>
+        <v>-0.9396918709462422</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9389354378479873</v>
+        <v>-0.9389354378479875</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9434621684850094</v>
+        <v>-0.9434621684850121</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8979441022401187</v>
+        <v>-0.8979441022401168</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9061851269134411</v>
+        <v>-0.9061851269134437</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9020126962291982</v>
+        <v>-0.902012696229198</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8964688289881806</v>
+        <v>-0.8964688289881808</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.877390028450997</v>
+        <v>-0.8773900284509969</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8844769598156319</v>
+        <v>-0.8844769598156318</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.497265547601114</v>
+        <v>-0.4972655476011157</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7464582972417426</v>
+        <v>-0.7464582972417428</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3138766166691078</v>
+        <v>-0.3138766166691064</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7097439402396347</v>
+        <v>-0.7097439402396344</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7008279533346528</v>
+        <v>-0.7008279533346526</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1003107812749877</v>
+        <v>-0.1003107812749871</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4897356932488058</v>
+        <v>-0.4897356932488059</v>
       </c>
       <c r="I9" t="n">
         <v>-0.6244070288647915</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3051432450669127</v>
+        <v>-0.3051432450669135</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4890822296360037</v>
+        <v>-0.489082229636003</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1902551367558222</v>
+        <v>-0.1902551367558237</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03458512261994424</v>
+        <v>-0.03458512261994402</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4870093307395665</v>
+        <v>-0.4870093307395671</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.531058418227971</v>
+        <v>-0.53105841822797</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.300861613199287</v>
+        <v>-0.3008616131992868</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.7284218193642852</v>
+        <v>-0.7284218193642849</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5672430857027694</v>
+        <v>-0.5672430857027692</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2666536042794132</v>
+        <v>-0.2666536042794125</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5376874610193941</v>
+        <v>-0.5376874610193947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3054529030035107</v>
+        <v>-0.3054529030035087</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6235143628054203</v>
+        <v>-0.6235143628054196</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2010746574172298</v>
+        <v>-0.2010746574172304</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1748054304516666</v>
+        <v>-0.1748054304516664</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.266356316682959</v>
+        <v>-0.2663563166829583</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.4922913846008471</v>
+        <v>-0.4922913846008474</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3756730017185332</v>
+        <v>-0.3756730017185342</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02549982605652623</v>
+        <v>0.02549982605652601</v>
       </c>
     </row>
     <row r="10">
@@ -5727,13 +5727,13 @@
         <v>-0.9131028927531256</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9195341572069943</v>
+        <v>-0.9195341572069942</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9232994174404858</v>
+        <v>-0.9232994174404857</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9105984073859849</v>
+        <v>-0.9105984073859847</v>
       </c>
       <c r="H10" t="n">
         <v>-0.9131028927531256</v>
@@ -5754,16 +5754,16 @@
         <v>-0.9131028927531027</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9224654881713565</v>
+        <v>-0.9224654881713564</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9198925656600137</v>
+        <v>-0.919892565660014</v>
       </c>
       <c r="P10" t="n">
         <v>-0.9205232511376934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9275546880723152</v>
+        <v>-0.927554688072315</v>
       </c>
       <c r="R10" t="n">
         <v>-0.9131028927531256</v>
@@ -5775,19 +5775,19 @@
         <v>-0.9131028927531256</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9190054979810155</v>
+        <v>-0.9190054979810154</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9164122159526983</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9131005190554859</v>
+        <v>-0.9131005190554858</v>
       </c>
       <c r="X10" t="n">
         <v>-0.9264477006202539</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.9011065388633177</v>
+        <v>-0.9011065388633176</v>
       </c>
       <c r="Z10" t="n">
         <v>-0.9254054118059569</v>
@@ -5796,7 +5796,7 @@
         <v>-0.9131028927531256</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.9004862436235298</v>
+        <v>-0.9004862436235296</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2765989603853891</v>
+        <v>-0.2765989603854065</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2619036231166389</v>
+        <v>-0.2619036231166491</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401900073339665</v>
+        <v>-0.3401900073339695</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.2653870301289586</v>
+        <v>-0.2653870301289775</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07506277282209402</v>
+        <v>-0.07506277282209747</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.197547347154147</v>
+        <v>-0.1975473471541578</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01507755098271593</v>
+        <v>0.0150775509827074</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1795013069071359</v>
+        <v>-0.17950130690715</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1751188725771665</v>
+        <v>-0.1751188725771656</v>
       </c>
       <c r="G12" t="n">
-        <v>0.120050590839785</v>
+        <v>0.1200505908397804</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.07136165789617809</v>
+        <v>-0.07136165789619195</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1375560445364068</v>
+        <v>-0.1375560445364153</v>
       </c>
       <c r="J12" t="n">
-        <v>0.008158294990361118</v>
+        <v>0.008158294990352193</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.07104046391051323</v>
+        <v>-0.07104046391052005</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07584065250679158</v>
+        <v>0.07584065250678561</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1523564237128015</v>
+        <v>0.1523564237127873</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.07002158138151097</v>
+        <v>-0.07002158138151926</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.09167282821157707</v>
+        <v>-0.0916728282115872</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02147475620730975</v>
+        <v>0.02147475620729766</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1886819595437343</v>
+        <v>-0.1886819595437387</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.1094585125839722</v>
+        <v>-0.1094585125839819</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03828886262629773</v>
+        <v>0.0382888626262921</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09493117134438289</v>
+        <v>-0.09493117134439302</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01921802049522667</v>
+        <v>0.01921802049521473</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2119202536694653</v>
+        <v>-0.2119202536694635</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07052258292170221</v>
+        <v>0.07052258292169143</v>
       </c>
       <c r="X12" t="n">
-        <v>0.08343457609786398</v>
+        <v>0.08343457609785543</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03843498704106373</v>
+        <v>0.03843498704105433</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.07261784519629098</v>
+        <v>-0.07261784519629841</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.01529694397732774</v>
+        <v>-0.01529694397733443</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.181889704167444</v>
+        <v>0.1818897041674361</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2853941275590714</v>
+        <v>-0.2853941275590859</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2826185342796556</v>
+        <v>-0.2826185342796656</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2844692554487713</v>
+        <v>-0.2844692554487734</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.278226385973809</v>
+        <v>-0.2782263859738184</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2906693344864192</v>
+        <v>-0.2906693344864288</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2794574042299783</v>
+        <v>-0.2794574042299945</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2840593580031188</v>
+        <v>-0.2840593580031302</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2827947011499578</v>
+        <v>-0.2827947011499616</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2831046991028781</v>
+        <v>-0.2831046991028912</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2865608291914218</v>
+        <v>-0.2865608291914231</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2823586848243549</v>
+        <v>-0.2823586848243543</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3558869979557844</v>
+        <v>-0.3558869979557875</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2794562374972289</v>
+        <v>-0.2794562374972375</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2860167167039845</v>
+        <v>-0.2860167167039976</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2735608911819642</v>
+        <v>-0.2735608911819657</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2855044052425496</v>
+        <v>-0.2855044052425567</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.2794574042299898</v>
+        <v>-0.2794574042300058</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.2732560002952273</v>
+        <v>-0.2732560002952306</v>
       </c>
     </row>
     <row r="14">
@@ -6164,79 +6164,79 @@
         <v>-0.8152503702072705</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6026254720704045</v>
+        <v>-0.602625472070405</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7972043299602587</v>
+        <v>-0.7972043299602585</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.79282189563028</v>
+        <v>-0.7928218956302802</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5294019782081913</v>
+        <v>-0.5294019782081925</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6890646809493005</v>
+        <v>-0.6890646809493004</v>
       </c>
       <c r="I15" t="n">
         <v>-0.7552590675895282</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6287337353052177</v>
+        <v>-0.6287337353052185</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6887434869636365</v>
+        <v>-0.6887434869636367</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5418623705463301</v>
+        <v>-0.541862370546331</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.465346599340322</v>
+        <v>-0.4653465993403219</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6877246044346328</v>
+        <v>-0.687724604434633</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7411253972595582</v>
+        <v>-0.7411253972595573</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6279778128406729</v>
+        <v>-0.6279778128406722</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.8063849825968523</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.7271615356370952</v>
+        <v>-0.7271615356370955</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5794141604268259</v>
+        <v>-0.5794141604268261</v>
       </c>
       <c r="T15" t="n">
         <v>-0.7126341943975055</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6302345485527521</v>
+        <v>-0.6302345485527522</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7844173704096762</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5789299861262789</v>
+        <v>-0.5789299861262782</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5660179929501151</v>
+        <v>-0.5660179929501148</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.5792680360120571</v>
+        <v>-0.579268036012057</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.6903208682494132</v>
+        <v>-0.6903208682494133</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6329999670304479</v>
+        <v>-0.6329999670304484</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.4358133188856773</v>
+        <v>-0.4358133188856771</v>
       </c>
     </row>
     <row r="16">
@@ -6255,13 +6255,13 @@
         <v>-0.8971604272831094</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9003215573327796</v>
+        <v>-0.9003215573327795</v>
       </c>
       <c r="F16" t="n">
         <v>-0.9021722785018894</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9276789550217878</v>
+        <v>-0.9276789550217877</v>
       </c>
       <c r="H16" t="n">
         <v>-0.8971604272831094</v>
@@ -6270,7 +6270,7 @@
         <v>-0.8971604272831094</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.927561364782007</v>
+        <v>-0.9275613647820069</v>
       </c>
       <c r="K16" t="n">
         <v>-0.8971604272831094</v>
@@ -6279,7 +6279,7 @@
         <v>-0.8971604272831094</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8971604272830982</v>
+        <v>-0.8971604272830981</v>
       </c>
       <c r="N16" t="n">
         <v>-0.9017623810562387</v>
@@ -6303,10 +6303,10 @@
         <v>-0.8971604272831094</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9318112538723298</v>
+        <v>-0.9318112538723297</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9283841146959954</v>
+        <v>-0.9283841146959952</v>
       </c>
       <c r="W16" t="n">
         <v>-0.928908806545205</v>
@@ -6318,13 +6318,13 @@
         <v>-0.8912639142350817</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.9032074282956636</v>
+        <v>-0.9032074282956634</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.8971604272831094</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.8909590233483476</v>
+        <v>-0.8909590233483479</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5819311424936265</v>
+        <v>-0.5819311424936261</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7344880090019876</v>
+        <v>-0.7344880090019877</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5356708011316365</v>
+        <v>-0.5356708011316393</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7975024503929492</v>
+        <v>-0.7975024503929489</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6860652336432796</v>
+        <v>-0.6860652336432803</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2757559722409646</v>
+        <v>-0.2757559722409679</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5722576387649264</v>
+        <v>-0.5722576387649263</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6459784140463503</v>
+        <v>-0.6459784140463511</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4091955217035502</v>
+        <v>-0.4091955217035521</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.454727583189602</v>
+        <v>-0.4547275831896022</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3545288237061117</v>
+        <v>-0.3545288237061135</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2257242602877922</v>
+        <v>-0.2257242602877934</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5799423237618762</v>
+        <v>-0.5799423237618767</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6425490566402812</v>
+        <v>-0.6425490566402818</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3874339260847177</v>
+        <v>-0.3874339260847184</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6889088771255233</v>
+        <v>-0.6889088771255242</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6359085406666062</v>
+        <v>-0.6359085406666075</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3816628507771415</v>
+        <v>-0.3816628507771423</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6035850398203683</v>
+        <v>-0.6035850398203692</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3134682942654279</v>
+        <v>-0.3134682942654297</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4873566254331698</v>
+        <v>-0.4873566254331703</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2603095103960734</v>
+        <v>-0.2603095103960735</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2051758446900523</v>
+        <v>-0.2051758446900537</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.06585688230954471</v>
+        <v>-0.06585688230954756</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5772056928362679</v>
+        <v>-0.5772056928362681</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3922691409334468</v>
+        <v>-0.3922691409334482</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.133620848832013</v>
+        <v>-0.1336208488320142</v>
       </c>
     </row>
     <row r="3">
@@ -6578,82 +6578,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9334909857672777</v>
+        <v>-0.9334909857672798</v>
       </c>
       <c r="C3" t="n">
         <v>-0.9235274354290786</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9304375463571183</v>
+        <v>-0.9304375463571185</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9328657711488801</v>
+        <v>-0.9328657711488803</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9205178507435859</v>
+        <v>-0.9205178507435846</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9233833616237966</v>
+        <v>-0.9233833616237963</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9227086403235703</v>
+        <v>-0.9227086403235704</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9310751417429691</v>
+        <v>-0.9310751417429709</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.928786197042251</v>
+        <v>-0.9287861970422516</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9293472726967811</v>
+        <v>-0.9293472726967809</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9356026380402683</v>
+        <v>-0.9356026380402682</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9280229072686598</v>
+        <v>-0.9280229072686594</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.927296681380175</v>
+        <v>-0.927296681380176</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9227438001135697</v>
+        <v>-0.9227438001135698</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9346178306657591</v>
+        <v>-0.9346178306657604</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.912117873127169</v>
+        <v>-0.9121178731271683</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9336905810319015</v>
+        <v>-0.9336905810319005</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9227459118231455</v>
+        <v>-0.9227459118231459</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.9103194670436224</v>
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06791391030980191</v>
+        <v>-0.06791391030978995</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1240157641676137</v>
+        <v>-0.1240157641676055</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05105255909971037</v>
+        <v>-0.05105255909971122</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.147739205666521</v>
+        <v>-0.1477392056665124</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1065360517896403</v>
+        <v>-0.1065360517896349</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04368334395692417</v>
+        <v>0.04368334395692549</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.06438803179270657</v>
+        <v>-0.06438803179270176</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0912583887097371</v>
+        <v>-0.09125838870973178</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01570519394682728</v>
+        <v>-0.01570519394682086</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.02154970664309407</v>
+        <v>-0.02154970664308976</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01497156459540308</v>
+        <v>0.0149715645954044</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06194300193746308</v>
+        <v>0.06194300193746778</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06718900923596773</v>
+        <v>-0.06718900923596607</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0900084282047728</v>
+        <v>-0.09000842820477455</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002978041169619479</v>
+        <v>0.002978041169619407</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.106906038387147</v>
+        <v>-0.1069060383871452</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.08758803810924348</v>
+        <v>-0.08758803810923871</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005081530351843141</v>
+        <v>0.005081530351843628</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0758065016125018</v>
+        <v>-0.07580650161250009</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02993764541945246</v>
+        <v>0.02993764541945306</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1034732429363783</v>
+        <v>-0.1034732429363793</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04931339791787542</v>
+        <v>0.04931339791788276</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06940897165553048</v>
+        <v>0.0694089716555303</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1201890974773723</v>
+        <v>0.1201890974773734</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.06619153939872746</v>
+        <v>-0.0661915393987281</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001215662135216394</v>
+        <v>0.001215662135226475</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09625401369759611</v>
+        <v>0.09625401369759296</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1960533449589438</v>
+        <v>-0.1960533449589428</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1929184152872694</v>
+        <v>-0.1929184152872639</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1961924871427517</v>
+        <v>-0.1961924871427442</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1964919496322025</v>
+        <v>-0.1964919496321938</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1913247895810508</v>
+        <v>-0.1913247895810436</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2031206236992997</v>
+        <v>-0.2031206236992971</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.192099620181777</v>
+        <v>-0.1920996201817684</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1951727981803547</v>
+        <v>-0.1951727981803495</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1943385047150901</v>
+        <v>-0.1943385047150858</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1945430102026835</v>
+        <v>-0.194543010202682</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1968230174161761</v>
+        <v>-0.1968230174161651</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1940602945556166</v>
+        <v>-0.1940602945556067</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2638262272921035</v>
+        <v>-0.2638262272921029</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1921361219879934</v>
+        <v>-0.1921361219879838</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.19646406669236</v>
+        <v>-0.1964640666923573</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1882630963773848</v>
+        <v>-0.1882630963773753</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1961260950891335</v>
+        <v>-0.196126095089136</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1921368916813372</v>
+        <v>-0.1921368916813326</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1868435121848872</v>
+        <v>-0.1868435121848891</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7791966558076615</v>
+        <v>-0.7791966558076618</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8352985096654725</v>
+        <v>-0.8352985096654726</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.76233530459757</v>
+        <v>-0.7623353045975724</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8590219511643798</v>
+        <v>-0.8590219511643796</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8178187972874977</v>
+        <v>-0.817818797287498</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7045014560477428</v>
+        <v>-0.7045014560477449</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7756707772905663</v>
+        <v>-0.7756707772905665</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8025411342075959</v>
+        <v>-0.8025411342075973</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7519761264391743</v>
+        <v>-0.7519761264391736</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7328324521409527</v>
+        <v>-0.7328324521409519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6963111809024572</v>
+        <v>-0.6963111809024588</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.649339743560397</v>
+        <v>-0.6493397435603975</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.778471754733827</v>
+        <v>-0.7784717547338285</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8381932282094399</v>
+        <v>-0.8381932282094414</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7452067588350475</v>
+        <v>-0.7452067588350498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8181887838850055</v>
+        <v>-0.818188783885007</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7988707836071024</v>
+        <v>-0.7988707836071036</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7062012151460153</v>
+        <v>-0.7062012151460167</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7870892471103595</v>
+        <v>-0.7870892471103607</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7182471545852156</v>
+        <v>-0.7182471545852173</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7801282695279588</v>
+        <v>-0.7801282695279596</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6988714020867927</v>
+        <v>-0.6988714020867905</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.678775828349136</v>
+        <v>-0.6787758283491377</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5910936480204853</v>
+        <v>-0.5910936480204876</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7774742848965857</v>
+        <v>-0.7774742848965868</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7100670833626411</v>
+        <v>-0.7100670833626405</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.6150287318002605</v>
+        <v>-0.6150287318002609</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9073360904568025</v>
+        <v>-0.907336090456802</v>
       </c>
       <c r="C7" t="n">
         <v>-0.9042011607851284</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9074752326406108</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9077746951300603</v>
+        <v>-0.9077746951300604</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9395095895857184</v>
+        <v>-0.9395095895857185</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9393915561916469</v>
+        <v>-0.9393915561916465</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9033823656796349</v>
+        <v>-0.903382365679635</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9064555436782152</v>
+        <v>-0.9064555436782178</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9425233047197573</v>
+        <v>-0.9425233047197588</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9427278102073507</v>
+        <v>-0.9427278102073517</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9081057629140351</v>
+        <v>-0.9081057629140356</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9422450945602845</v>
+        <v>-0.9422450945602853</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9404812538836831</v>
+        <v>-0.9404812538836828</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.94032092199266</v>
+        <v>-0.9403209219926593</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9446488666970271</v>
+        <v>-0.9446488666970296</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8995458418752433</v>
+        <v>-0.8995458418752436</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9074088405869923</v>
+        <v>-0.9074088405869948</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.903419637179195</v>
+        <v>-0.9034196371791942</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8981262576827453</v>
+        <v>-0.8981262576827455</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8833568054036651</v>
+        <v>-0.883356805403665</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8883150532646424</v>
+        <v>-0.8883150532646426</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5486535368719621</v>
+        <v>-0.5486535368719612</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7117669516741451</v>
+        <v>-0.7117669516741453</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4989374096989219</v>
+        <v>-0.498937409698923</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7782112865746452</v>
+        <v>-0.7782112865746449</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6594396694673386</v>
+        <v>-0.6594396694673402</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2196061659847328</v>
+        <v>-0.2196061659847355</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5382573934924395</v>
+        <v>-0.53825739349244</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.61748533110117</v>
+        <v>-0.6174853311011701</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3623289795492773</v>
+        <v>-0.3623289795492785</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4119474913688393</v>
+        <v>-0.4119474913688399</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3042635849730412</v>
+        <v>-0.3042635849730407</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1658769913535339</v>
+        <v>-0.1658769913535347</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5465161474346877</v>
+        <v>-0.5465161474346879</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6137997904436167</v>
+        <v>-0.6137997904436175</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3396267968805314</v>
+        <v>-0.3396267968805312</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.663622828127844</v>
+        <v>-0.6636228281278435</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.6066632080725867</v>
+        <v>-0.6066632080725869</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3334246049928525</v>
+        <v>-0.3334246049928533</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5719250450708366</v>
+        <v>-0.5719250450708364</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.26013571121847</v>
+        <v>-0.2601357112184718</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.445317959524289</v>
+        <v>-0.4453179595242895</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2030058072574836</v>
+        <v>-0.2030058072574843</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1437534918820364</v>
+        <v>-0.1437534918820368</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005973013530575793</v>
+        <v>0.005973013530573596</v>
       </c>
       <c r="Z9" t="n">
         <v>-0.5435750819968301</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3448232167350088</v>
+        <v>-0.3448232167350083</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.06814525709809356</v>
+        <v>-0.06814525709809512</v>
       </c>
     </row>
     <row r="10">
@@ -7197,34 +7197,34 @@
         <v>-0.926475951548043</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9210770316628394</v>
+        <v>-0.9210770316628393</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9246769450202751</v>
+        <v>-0.9246769450202752</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9125336845504017</v>
+        <v>-0.9125336845504018</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="M10" t="n">
         <v>-0.9149281884541399</v>
@@ -7233,43 +7233,43 @@
         <v>-0.9238796367521162</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9214197010386617</v>
+        <v>-0.9214197010386618</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9220226907221151</v>
+        <v>-0.9220226907221153</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9287453505593416</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="U10" t="n">
         <v>-0.920599391236864</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.918122853003674</v>
+        <v>-0.9181228530036741</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9149259189935699</v>
+        <v>-0.91492591899357</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9276869751295339</v>
+        <v>-0.9276869751295341</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.9035062034913968</v>
+        <v>-0.903506203491397</v>
       </c>
       <c r="Z10" t="n">
         <v>-0.9266904571756932</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9149281884541646</v>
+        <v>-0.9149281884541647</v>
       </c>
       <c r="AB10" t="n">
         <v>-0.902865584299581</v>
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2825129804327686</v>
+        <v>-0.2825129804327662</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228092</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2711793745927544</v>
+        <v>-0.2711793745927484</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3329714983970322</v>
+        <v>-0.33297149839703</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.2736164795228166</v>
+        <v>-0.2736164795228099</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1066642053802667</v>
+        <v>-0.106664205380265</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1868385973266845</v>
+        <v>-0.1868385973266785</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08222746441163907</v>
+        <v>-0.08222746441163047</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2194976778529067</v>
+        <v>-0.2194976778528993</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1611184072477299</v>
+        <v>-0.161118407247722</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05507094628978387</v>
+        <v>0.05507094628979035</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1015542364972549</v>
+        <v>-0.1015542364972474</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1404967828883799</v>
+        <v>-0.1404967828883793</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02397744745066974</v>
+        <v>-0.02397744745066654</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.03946970708039204</v>
+        <v>-0.03946970708038301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0134596717090128</v>
+        <v>0.01345967170901929</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08148020215058042</v>
+        <v>0.08148020215058707</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1056136241102128</v>
+        <v>-0.105613624110204</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1386852459184028</v>
+        <v>-0.1386852459183968</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.003922246359428678</v>
+        <v>-0.003922246359421978</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1631745361224054</v>
+        <v>-0.1631745361223987</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.135177434173633</v>
+        <v>-0.1351774341736356</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0008737113021942871</v>
+        <v>-0.0008737113021873126</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1181027435396411</v>
+        <v>-0.1181027435396343</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03514964399272517</v>
+        <v>0.0351496439927331</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.115227159786149</v>
+        <v>-0.1152271597861532</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06323044481210757</v>
+        <v>0.06323044481210499</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0923544648223882</v>
+        <v>0.09235446482239484</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1659488503257285</v>
+        <v>0.1659488503257324</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.1041680156454451</v>
+        <v>-0.1041680156454364</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.006476418881879912</v>
+        <v>-0.006476418881870163</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.129517835212838</v>
+        <v>0.1295178352128451</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2923735316004202</v>
+        <v>-0.2923735316004182</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2897198251625509</v>
+        <v>-0.2897198251625461</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2914892741367036</v>
+        <v>-0.2914892741367014</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2855205527682017</v>
+        <v>-0.2855205527681955</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2955940132478537</v>
+        <v>-0.2955940132478512</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2866975123378873</v>
+        <v>-0.2866975123378843</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2910973768444347</v>
+        <v>-0.2910973768444358</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2898882558761041</v>
+        <v>-0.2898882558761027</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2901846406417563</v>
+        <v>-0.2901846406417501</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2934889989335979</v>
+        <v>-0.2934889989335918</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2894850527450396</v>
+        <v>-0.2894850527450358</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3476227900902089</v>
+        <v>-0.3476227900902095</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2866963968402964</v>
+        <v>-0.2866963968402936</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2929687804914876</v>
+        <v>-0.2929687804914852</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2810833162258149</v>
+        <v>-0.2810833162258097</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2924789665720749</v>
+        <v>-0.2924789665720725</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.2866975123378996</v>
+        <v>-0.2866975123378964</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.280768435599748</v>
+        <v>-0.2807684355997382</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9156121635936463</v>
+        <v>-0.9156121635936464</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521512</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="S14" t="n">
         <v>-0.88279191682209</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9148086140024729</v>
+        <v>-0.9148086140024732</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9169600872296316</v>
+        <v>-0.9169600872296318</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.8852290217521509</v>
+        <v>-0.8852290217521513</v>
       </c>
     </row>
     <row r="15">
@@ -7634,76 +7634,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.718276747609603</v>
+        <v>-0.7182767476096024</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.7984511395560201</v>
+        <v>-0.7984511395560202</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6938400066409746</v>
+        <v>-0.6938400066409753</v>
       </c>
       <c r="E15" t="n">
         <v>-0.8311102200822433</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7727309494770671</v>
+        <v>-0.7727309494770677</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5882726614170346</v>
+        <v>-0.5882726614170358</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7131667787265905</v>
+        <v>-0.7131667787265906</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7521093251177151</v>
+        <v>-0.752109325117715</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6570766306115471</v>
+        <v>-0.6570766306115473</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6510822493097278</v>
+        <v>-0.6510822493097279</v>
       </c>
       <c r="L15" t="n">
         <v>-0.5981528705203238</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.530132340078755</v>
+        <v>-0.530132340078756</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7172261663395463</v>
+        <v>-0.7172261663395465</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7820288536252196</v>
+        <v>-0.7820288536252199</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6472658540662469</v>
+        <v>-0.6472658540662474</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7747870783517402</v>
+        <v>-0.7747870783517404</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.7467899764029683</v>
+        <v>-0.7467899764029678</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6124862535315294</v>
+        <v>-0.6124862535315299</v>
       </c>
       <c r="T15" t="n">
         <v>-0.7297152857689779</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6081939637140911</v>
+        <v>-0.6081939637140913</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6970642753915961</v>
+        <v>-0.6970642753915964</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5801131628947095</v>
+        <v>-0.5801131628947106</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5509891428844294</v>
+        <v>-0.5509891428844292</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.4456636919036086</v>
+        <v>-0.4456636919036104</v>
       </c>
       <c r="Z15" t="n">
         <v>-0.7157805578747808</v>
@@ -7712,7 +7712,7 @@
         <v>-0.6180889611112161</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.482094707016499</v>
+        <v>-0.4820947070164992</v>
       </c>
     </row>
     <row r="16">
@@ -7725,82 +7725,82 @@
         <v>-0.9039860738297572</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9013323673918865</v>
+        <v>-0.9013323673918866</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9031018163660387</v>
+        <v>-0.9031018163660391</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9288641604750177</v>
+        <v>-0.9288641604750179</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9286931964087302</v>
+        <v>-0.9286931964087303</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8983100545672228</v>
+        <v>-0.8983100545672229</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9027099190737712</v>
+        <v>-0.9027099190737713</v>
       </c>
       <c r="O16" t="n">
         <v>-0.9332318635829203</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9335282483485724</v>
+        <v>-0.9335282483485725</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9051015411629334</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="U16" t="n">
         <v>-0.9328286604518561</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9294599056956528</v>
+        <v>-0.929459905695653</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9300400045471124</v>
+        <v>-0.9300400045471126</v>
       </c>
       <c r="X16" t="n">
         <v>-0.936312388198303</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.8926958584551519</v>
+        <v>-0.892695858455152</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.9040915088014105</v>
+        <v>-0.9040915088014108</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.898310054567235</v>
+        <v>-0.8983100545672351</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.8923809778290834</v>
+        <v>-0.8923809778290837</v>
       </c>
     </row>
   </sheetData>
@@ -9469,7 +9469,7 @@
         <v>-0.9070031580780623</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.997794772665865</v>
+        <v>-0.9977947726658649</v>
       </c>
       <c r="L2" t="n">
         <v>-1.283893895208308</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.316269852401649</v>
+        <v>-0.3162698524016491</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2535233946743478</v>
@@ -9648,7 +9648,7 @@
         <v>-0.2684849079290992</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3727646785503044</v>
+        <v>-0.3727646785503045</v>
       </c>
       <c r="M4" t="n">
         <v>-0.2591252428458469</v>
@@ -9678,10 +9678,10 @@
         <v>-0.2405004505462271</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2963167376386467</v>
+        <v>-0.2963167376386466</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1350335058457221</v>
+        <v>-0.135033505845722</v>
       </c>
       <c r="X4" t="n">
         <v>0.00266037591741986</v>
@@ -9775,10 +9775,10 @@
         <v>-0.251178402144152</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2461859722830028</v>
+        <v>-0.2461859722830027</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2509709721410416</v>
+        <v>-0.2509709721410415</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.2485225993467438</v>
@@ -10325,7 +10325,7 @@
         <v>-0.4363796267880119</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3457711318583155</v>
+        <v>-0.3457711318583156</v>
       </c>
       <c r="D12" t="n">
         <v>-0.3171928737749193</v>
@@ -10364,7 +10364,7 @@
         <v>-0.3496398646983961</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4376936712356032</v>
+        <v>-0.437693671235603</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.3377203142299673</v>
@@ -10388,7 +10388,7 @@
         <v>-0.1737182540602537</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02583809701064858</v>
+        <v>0.02583809701064836</v>
       </c>
       <c r="Y12" t="n">
         <v>-0.2287292491217923</v>
@@ -10397,10 +10397,10 @@
         <v>-0.3362440483772047</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.07404251339245846</v>
+        <v>-0.07404251339245857</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.3460358502184331</v>
+        <v>-0.346035850218433</v>
       </c>
     </row>
     <row r="13">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.341678857419248</v>
+        <v>-0.3416788574192479</v>
       </c>
       <c r="C13" t="n">
         <v>-0.3381952017314988</v>
@@ -10476,7 +10476,7 @@
         <v>-0.3381945170923618</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3420441913062626</v>
+        <v>-0.3420441913062625</v>
       </c>
       <c r="Y13" t="n">
         <v>-0.3348087856853968</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide climate change results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide climate change results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3007025587490835</v>
+        <v>-0.3007025587490874</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7657015346968569</v>
+        <v>-0.7657015346968571</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4823293551572307</v>
+        <v>-0.4823293551572318</v>
       </c>
       <c r="E2" t="n">
         <v>-0.7390134411612413</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.580263790371529</v>
+        <v>-0.5802637903715292</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.08964370178878349</v>
+        <v>-0.08964370178878493</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3235042251250899</v>
+        <v>-0.3235042251250917</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5599168723320608</v>
+        <v>-0.559916872332058</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2977128348130732</v>
+        <v>-0.2977128348130729</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3402173487689732</v>
+        <v>-0.3402173487689747</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.04810848733027453</v>
+        <v>-0.04810848733027896</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08440431401430916</v>
+        <v>0.08440431401430906</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2872408061156917</v>
+        <v>-0.287240806115694</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3780006401560994</v>
+        <v>-0.3780006401561006</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4019289862295904</v>
+        <v>-0.4019289862295914</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4741866514268698</v>
+        <v>-0.474186651426871</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5498296768716038</v>
+        <v>-0.5498296768716051</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2274299051838853</v>
+        <v>-0.227429905183886</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4008766635131644</v>
+        <v>-0.4008766635131657</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09753720287677618</v>
+        <v>-0.09753720287677663</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6277151169185112</v>
+        <v>-0.627715116918512</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2297551550051051</v>
+        <v>-0.2297551550051068</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3985049748660242</v>
+        <v>-0.3985049748660248</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4521112776413763</v>
+        <v>-0.4521112776413788</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4481157284317313</v>
+        <v>-0.4481157284317336</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2604214544484438</v>
+        <v>-0.2604214544484467</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04845348002035195</v>
+        <v>0.04845348002035151</v>
       </c>
     </row>
     <row r="3">
@@ -674,37 +674,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.927289188399679</v>
+        <v>-0.9272891883996767</v>
       </c>
       <c r="C3" t="n">
         <v>-0.9159598928733771</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9238723146533463</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.926611749374919</v>
+        <v>-0.9266117493749191</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9119860238323551</v>
+        <v>-0.9119860238323573</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9156196526786166</v>
+        <v>-0.9156196526786183</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="M3" t="n">
         <v>-0.9143050632539329</v>
@@ -713,46 +713,46 @@
         <v>-0.9244394486416844</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9217393998595329</v>
+        <v>-0.9217393998595398</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9224012470578341</v>
+        <v>-0.9224012470578371</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9297801022899468</v>
+        <v>-0.9297801022899486</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9207850635495184</v>
+        <v>-0.9207850635495145</v>
       </c>
       <c r="V3" t="n">
         <v>-0.920572323850571</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9146117630624079</v>
+        <v>-0.9146117630624104</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9286184193763546</v>
+        <v>-0.9286184193763531</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9019850711027282</v>
+        <v>-0.901985071102728</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.927524631811924</v>
+        <v>-0.9275246318119243</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9146142540405562</v>
+        <v>-0.9146142540405591</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9001480801454478</v>
+        <v>-0.9001480801454476</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.052457740304511</v>
+        <v>0.05245774030450862</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1178840954143444</v>
+        <v>-0.1178840954143468</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01374309421673629</v>
+        <v>-0.01374309421673964</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1088959486988479</v>
+        <v>-0.1088959486988502</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05026341109778384</v>
+        <v>-0.05026341109778607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1293862152883129</v>
+        <v>0.1293862152883098</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04414680066114086</v>
+        <v>0.04414680066113758</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04202283314833582</v>
+        <v>-0.04202283314833957</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03937743487547994</v>
+        <v>0.03937743487547825</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03805506334835455</v>
+        <v>0.03805506334835122</v>
       </c>
       <c r="L4" t="n">
-        <v>0.144525313227328</v>
+        <v>0.1445253132273242</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1930211676491526</v>
+        <v>0.1930211676491503</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05736439106350148</v>
+        <v>0.05736439106350288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02428349731155232</v>
+        <v>0.02428349731154953</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01556189614859023</v>
+        <v>0.01556189614858768</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.01077517432347473</v>
+        <v>-0.01077517432347794</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0383461688528292</v>
+        <v>-0.03834616885283202</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07916476211808694</v>
+        <v>0.07916476211808507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0159454554217312</v>
+        <v>0.01594545542172786</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1265091268319109</v>
+        <v>0.1265091268319084</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1586061918071234</v>
+        <v>-0.1586061918071239</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07831723586271522</v>
+        <v>0.07831723586271265</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0168099080838405</v>
+        <v>0.01680990808383576</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.002728959800788062</v>
+        <v>-0.002728959800795929</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.001272629031980854</v>
+        <v>-0.001272629031984584</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.06713972981748648</v>
+        <v>0.0671397298174828</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1805002460512093</v>
+        <v>0.1805002460512073</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1759257284514486</v>
+        <v>-0.1759257284514526</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1726515025469615</v>
+        <v>-0.1726515025469633</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1762748373642317</v>
+        <v>-0.1762748373642344</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1765031751314501</v>
+        <v>-0.1765031751314522</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1703479046654892</v>
+        <v>-0.1703479046654935</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1858423444083218</v>
+        <v>-0.1858423444083211</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1709966729275204</v>
+        <v>-0.1709966729275234</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1748870317729929</v>
+        <v>-0.1748870317729989</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1739028956974719</v>
+        <v>-0.1739028956974773</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1741441312294511</v>
+        <v>-0.174144131229457</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.176833637314663</v>
+        <v>-0.1768336373146622</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1735550513188557</v>
+        <v>-0.1735550513188588</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2653492048309125</v>
+        <v>-0.265349204830913</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1713049557818573</v>
+        <v>-0.1713049557818592</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1764102175338284</v>
+        <v>-0.1764102175338344</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1667026748326567</v>
+        <v>-0.1667026748326615</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1760115448104948</v>
+        <v>-0.1760115448104974</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1713058637141414</v>
+        <v>-0.1713058637141415</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.16525388358732</v>
+        <v>-0.1652538835873223</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.6745774135422776</v>
+        <v>-0.6745774135422791</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8449192492611338</v>
+        <v>-0.8449192492611337</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7407782480635243</v>
+        <v>-0.7407782480635251</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8359311025456374</v>
+        <v>-0.8359311025456371</v>
       </c>
       <c r="F6" t="n">
         <v>-0.7772985649445736</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6346546387905011</v>
+        <v>-0.6346546387905024</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6828883531856467</v>
+        <v>-0.6828883531856483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7690579869951251</v>
+        <v>-0.7690579869951264</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7095605786801413</v>
+        <v>-0.7095605786801423</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6889800904984364</v>
+        <v>-0.6889800904984373</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5825098406194611</v>
+        <v>-0.5825098406194626</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5340139861976365</v>
+        <v>-0.5340139861976363</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6696707627832869</v>
+        <v>-0.6696707627832821</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7397573567672634</v>
+        <v>-0.7397573567672638</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7484789579302248</v>
+        <v>-0.7484789579302258</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.7378103281702634</v>
+        <v>-0.7378103281702638</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7653813226996178</v>
+        <v>-0.765381322699619</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6478703917287018</v>
+        <v>-0.6478703917287025</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7110896984250582</v>
+        <v>-0.7110896984250589</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6375317272469054</v>
+        <v>-0.6375317272469058</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.829862641749027</v>
+        <v>-0.8298626417490269</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6857236182161016</v>
+        <v>-0.6857236182161018</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7472309459949762</v>
+        <v>-0.7472309459949782</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.729764113647577</v>
+        <v>-0.7297641136475819</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7283077828787693</v>
+        <v>-0.7283077828787697</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6598954240293025</v>
+        <v>-0.6598954240293032</v>
       </c>
       <c r="AB6" t="n">
         <v>-0.5465349077955796</v>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9029608822982372</v>
+        <v>-0.9029608822982381</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8996866563937518</v>
+        <v>-0.8996866563937517</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9033099912110218</v>
@@ -1041,67 +1041,67 @@
         <v>-0.9035383289782392</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9343887587443054</v>
+        <v>-0.9343887587443067</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9347803579639453</v>
+        <v>-0.9347803579639443</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="M7" t="n">
         <v>-0.8980318267743097</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9019221856197819</v>
+        <v>-0.9019221856197854</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9379437497762881</v>
+        <v>-0.9379437497762916</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9381849853082668</v>
+        <v>-0.9381849853082699</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9038687911614522</v>
+        <v>-0.90386879116145</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9375959053976708</v>
+        <v>-0.9375959053976717</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9366056547728162</v>
+        <v>-0.936605654772816</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9353458098606731</v>
+        <v>-0.9353458098606733</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9404510716126441</v>
+        <v>-0.9404510716126483</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8937378286794456</v>
+        <v>-0.8937378286794482</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9030466986572846</v>
+        <v>-0.9030466986572848</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.8983410175609309</v>
+        <v>-0.8983410175609294</v>
       </c>
       <c r="AB7" t="n">
         <v>-0.892289037434109</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.004724434620318</v>
+        <v>-1.004724434620323</v>
       </c>
       <c r="C2" t="n">
         <v>-1.019522346936239</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9352931639840797</v>
+        <v>-0.9352931639840854</v>
       </c>
       <c r="E2" t="n">
         <v>-0.9793794565239206</v>
@@ -1285,70 +1285,70 @@
         <v>-1.204176086103346</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8581984108179382</v>
+        <v>-0.8581984108179419</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.874590673685707</v>
+        <v>-0.8745906736857122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9720623419770398</v>
+        <v>-0.9720623419770443</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9207225359620559</v>
+        <v>-0.9207225359620582</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9774236384011658</v>
+        <v>-0.9774236384011704</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.413921205056865</v>
+        <v>-1.413921205056876</v>
       </c>
       <c r="M2" t="n">
         <v>-1.001956401294701</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9832142682337857</v>
+        <v>-0.9832142682337836</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.12287855197152</v>
+        <v>-1.122878551971527</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.003438044481352</v>
+        <v>-1.003438044481353</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9451418443581799</v>
+        <v>-0.9451418443581846</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.624245889677151</v>
+        <v>-1.624245889677155</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.165113927192913</v>
+        <v>-1.165113927192917</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.092850858770426</v>
+        <v>-1.092850858770428</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.864886257580155</v>
+        <v>-0.8648862575801596</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7993455426132591</v>
+        <v>-0.7993455426132589</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3983530152151949</v>
+        <v>-0.3983530152151996</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1662630949181741</v>
+        <v>-0.1662630949181794</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.5045766475388278</v>
+        <v>-0.5045766475388336</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.835689489416359</v>
+        <v>-0.8356894894163646</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3319356561499897</v>
+        <v>-0.3319356561499981</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.926886214545975</v>
+        <v>-0.9268862145459749</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9479289245624455</v>
+        <v>-0.9479289245624519</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9410414484777515</v>
+        <v>-0.9410414484777516</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9452954267602575</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.948071003113453</v>
+        <v>-0.9480710031134532</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9394113362789752</v>
+        <v>-0.9394113362789765</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9410660441645885</v>
+        <v>-0.9410660441645932</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9414903444867944</v>
+        <v>-0.9414903444867946</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9463427879247636</v>
+        <v>-0.9463427879247689</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9448399677853468</v>
+        <v>-0.9448399677853512</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9452083453147722</v>
+        <v>-0.9452083453147806</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9493153423126275</v>
+        <v>-0.9493153423126318</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9443782045810104</v>
+        <v>-0.9443782045810143</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.943265609336946</v>
+        <v>-0.9432656093369461</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9408727964576437</v>
+        <v>-0.9408727964576484</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9486687612227211</v>
+        <v>-0.9486687612227307</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9339636477991378</v>
+        <v>-0.9339636477991403</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9480599700105379</v>
+        <v>-0.9480599700105444</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9408741829165828</v>
+        <v>-0.9408741829165835</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9334499166060145</v>
+        <v>-0.9334499166060146</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2696733733540888</v>
+        <v>-0.2696733733540937</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2751733378556442</v>
+        <v>-0.2751733378556382</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2443664905103208</v>
+        <v>-0.2443664905103284</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2608579159432909</v>
+        <v>-0.2608579159432872</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.343159907655591</v>
+        <v>-0.3431599076555877</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2162663582735604</v>
+        <v>-0.2162663582735693</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2222411456011941</v>
+        <v>-0.2222411456011988</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2577684241232676</v>
+        <v>-0.2577684241232731</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2476859044812869</v>
+        <v>-0.2476859044812857</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2597225537143418</v>
+        <v>-0.2597225537143473</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4188207911471392</v>
+        <v>-0.4188207911471442</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2690560356240118</v>
+        <v>-0.26905603562401</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2618331702913265</v>
+        <v>-0.261833170291325</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3127391616929069</v>
+        <v>-0.3127391616929127</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2692044992539922</v>
+        <v>-0.269204499253994</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2479562188576371</v>
+        <v>-0.2479562188576422</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4954816689340905</v>
+        <v>-0.495481668934097</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3281334600082902</v>
+        <v>-0.3281334600082927</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3017944201240843</v>
+        <v>-0.301794420124087</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2187039998857267</v>
+        <v>-0.2187039998857318</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2518322265374574</v>
+        <v>-0.2518322265374568</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.04865811135361822</v>
+        <v>-0.04865811135362508</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03593593925720347</v>
+        <v>0.0359359392571995</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.08737537799471952</v>
+        <v>-0.08737537799472286</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2080621207357847</v>
+        <v>-0.2080621207357896</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.02444976388635795</v>
+        <v>-0.02444976388636396</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2412673038059967</v>
+        <v>-0.2412673038059946</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2489720768645459</v>
+        <v>-0.2489720768645479</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2465679719367587</v>
+        <v>-0.2465679719367572</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2484346873293156</v>
+        <v>-0.2484346873293174</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2498126122434947</v>
+        <v>-0.2498126122434906</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2458675159537929</v>
+        <v>-0.2458675159537941</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2551008743355772</v>
+        <v>-0.2551008743355763</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2470168679458138</v>
+        <v>-0.2470168679458149</v>
       </c>
       <c r="N5" t="n">
         <v>-0.2483939486854713</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2478461883916495</v>
+        <v>-0.2478461883916573</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2479804576754206</v>
+        <v>-0.2479804576754287</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2494774098543507</v>
+        <v>-0.2494774098543501</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2476778811259738</v>
+        <v>-0.2476778811259746</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3042894008634937</v>
+        <v>-0.3042894008634935</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2464002010275866</v>
+        <v>-0.2464002010275888</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2492417386396167</v>
+        <v>-0.2492417386396211</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2438818974728758</v>
+        <v>-0.243881897472882</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2490198413915664</v>
+        <v>-0.2490198413915655</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2464007063755908</v>
+        <v>-0.2464007063755895</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2436596961320021</v>
+        <v>-0.2436596961319977</v>
       </c>
     </row>
     <row r="6">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9389283774174154</v>
+        <v>-0.9389283774174224</v>
       </c>
       <c r="C6" t="n">
         <v>-0.9444283419189652</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9136214945736492</v>
+        <v>-0.9136214945736538</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9301129200066143</v>
@@ -1637,67 +1637,67 @@
         <v>-1.012414911718914</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9222793167028698</v>
+        <v>-0.9222793167028783</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8914961496645213</v>
+        <v>-0.8914961496645286</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.927023428186596</v>
+        <v>-0.9270234281866035</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9436287431945396</v>
+        <v>-0.9436287431945406</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9289775577776691</v>
+        <v>-0.9289775577776763</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.088075795210464</v>
+        <v>-1.088075795210465</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9383110396873363</v>
+        <v>-0.938311039687337</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9310881743546496</v>
+        <v>-0.9310881743546553</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.018752120122215</v>
+        <v>-1.018752120122219</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9752174576833011</v>
+        <v>-0.9752174576833021</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9172112229209647</v>
+        <v>-0.9172112229209718</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.164736672997417</v>
+        <v>-1.164736672997425</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9973884640716151</v>
+        <v>-0.997388464071623</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9710494241874106</v>
+        <v>-0.971049424187417</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9247169583150359</v>
+        <v>-0.9247169583150403</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8985868104978825</v>
+        <v>-0.8985868104978821</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7546710697829269</v>
+        <v>-0.754671069782933</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6700770191721048</v>
+        <v>-0.670077019172109</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.7566303820580449</v>
+        <v>-0.7566303820580508</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8773171247991142</v>
+        <v>-0.8773171247991198</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6937047679496872</v>
+        <v>-0.6937047679496883</v>
       </c>
       <c r="AB6" t="n">
         <v>-0.9105223078693208</v>
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9182270809278741</v>
+        <v>-0.9182270809278801</v>
       </c>
       <c r="C7" t="n">
         <v>-0.9158229760000844</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9176896913926436</v>
+        <v>-0.9176896913926437</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9190676163068168</v>
+        <v>-0.9190676163068169</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.951880474383099</v>
+        <v>-0.9518804743831022</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9510437130488257</v>
+        <v>-0.9510437130488311</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9162718720091414</v>
+        <v>-0.9162718720091421</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9176489527487933</v>
+        <v>-0.9176489527488008</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9538591468209592</v>
+        <v>-0.9538591468209664</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9539934161047282</v>
+        <v>-0.9539934161047359</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9187324139176751</v>
+        <v>-0.918732413917681</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9536908395552824</v>
+        <v>-0.9536908395552827</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9510439848239186</v>
+        <v>-0.9510439848239184</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9524131594568934</v>
+        <v>-0.9524131594568963</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9552546970689219</v>
+        <v>-0.9552546970689285</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.913136901536201</v>
+        <v>-0.9131369015362117</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9182748454548907</v>
+        <v>-0.9182748454548957</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.915655710438916</v>
+        <v>-0.9156557104389191</v>
       </c>
       <c r="AB7" t="n">
         <v>-0.9129147001953241</v>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4237228182927339</v>
+        <v>-0.4237228182927277</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.804141004409015</v>
+        <v>-0.8041410044090137</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4266224668523171</v>
+        <v>-0.4266224668523179</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7427355357925346</v>
+        <v>-0.7427355357925315</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6538178770244943</v>
+        <v>-0.6538178770244938</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1185313148138508</v>
+        <v>-0.1185313148138537</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4584803484635992</v>
+        <v>-0.4584803484635993</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.641302541816948</v>
+        <v>-0.6413025418169485</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.323027817357055</v>
+        <v>-0.3230278173570597</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4163508039154895</v>
+        <v>-0.4163508039154896</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1355281010007126</v>
+        <v>-0.1355281010006885</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009186451267592263</v>
+        <v>0.009186451267591177</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.389994344788761</v>
+        <v>-0.3899943447887609</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4709962218669704</v>
+        <v>-0.4709962218669703</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3421226691065816</v>
+        <v>-0.3421226691065806</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5604734365785214</v>
+        <v>-0.5604734365785221</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5449329137272583</v>
+        <v>-0.5449329137272577</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2649103707189393</v>
+        <v>-0.2649103707189379</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5208556984725021</v>
+        <v>-0.5208556984725017</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2218942222440632</v>
+        <v>-0.221894222244064</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7344507753264294</v>
+        <v>-0.7344507753264304</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1960767584672178</v>
+        <v>-0.1960767584672176</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3666033892869352</v>
+        <v>-0.366603389286939</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4807294680982956</v>
+        <v>-0.4807294680982943</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5358878919853275</v>
+        <v>-0.5358878919853262</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3978447351913017</v>
+        <v>-0.3978447351912995</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01716014218417444</v>
+        <v>0.01716014218418245</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9298412594368479</v>
+        <v>-0.9298412594368523</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9190484837895554</v>
+        <v>-0.9190484837895562</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9264584419301012</v>
+        <v>-0.9264584419301011</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.929237587229643</v>
+        <v>-0.9292375872296429</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9153725846582653</v>
+        <v>-0.915372584658267</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9188084265569295</v>
+        <v>-0.9188084265569294</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9174749175142786</v>
+        <v>-0.9174749175142785</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9271469175193736</v>
+        <v>-0.9271469175193744</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9245941038482109</v>
+        <v>-0.9245941038482171</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9252198601631755</v>
+        <v>-0.9252198601631765</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9321963424540662</v>
+        <v>-0.9321963424540709</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9236880278005011</v>
+        <v>-0.9236880278005047</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9235019576954514</v>
+        <v>-0.9235019576954503</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9178551409162951</v>
+        <v>-0.9178551409162955</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9310980067337737</v>
+        <v>-0.9310980067337747</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9059105224170454</v>
+        <v>-0.9059105224170499</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9300638639933367</v>
+        <v>-0.9300638639933402</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9178574960606283</v>
+        <v>-0.9178574960606287</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9039344625075499</v>
+        <v>-0.9039344625075498</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001592275260584477</v>
+        <v>0.001592275260583276</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1378225731699405</v>
+        <v>-0.1378225731699421</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005353874100096252</v>
+        <v>0.0005353874100089522</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1160949155835965</v>
+        <v>-0.1160949155835961</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08307748707106001</v>
+        <v>-0.08307748707106068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1128309945390689</v>
+        <v>0.1128309945390687</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01107643634317194</v>
+        <v>-0.01107643634317228</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07771297901388276</v>
+        <v>-0.0777129790138841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02349968949814767</v>
+        <v>0.02349968949814483</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004279287934527755</v>
+        <v>0.004279287934527226</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1066358655602981</v>
+        <v>0.1066358655602979</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1596257536966907</v>
+        <v>0.1596257536966906</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01388590779305217</v>
+        <v>0.01388590779305271</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01563832522989221</v>
+        <v>-0.01563832522989388</v>
       </c>
       <c r="P4" t="n">
-        <v>0.031334571441609</v>
+        <v>0.03133457144160894</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0482517192977521</v>
+        <v>-0.04825171929775167</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.04258738120449765</v>
+        <v>-0.04258738120449883</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0594775475313208</v>
+        <v>0.05947754753131946</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.03381151897307547</v>
+        <v>-0.03381151897307647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07515642852929422</v>
+        <v>0.07515642852929388</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2078577416816389</v>
+        <v>-0.207857741681637</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08456659091199013</v>
+        <v>0.08456659091198908</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02241163640299909</v>
+        <v>0.02241163640300049</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.01918597918766244</v>
+        <v>-0.0191859791876629</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.03929057699157084</v>
+        <v>-0.03929057699157253</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01102453267526451</v>
+        <v>0.01102453267526447</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.163181825300671</v>
+        <v>0.1631818253006717</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1828819533936522</v>
+        <v>-0.182881953393653</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1797050000924002</v>
+        <v>-0.1797050000924048</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1830597574874558</v>
+        <v>-0.1830597574874567</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1834647372993139</v>
+        <v>-0.1834647372993149</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1776082913366159</v>
+        <v>-0.1776082913366184</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1936553465460799</v>
+        <v>-0.1936553465460819</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1781314338171298</v>
+        <v>-0.1781314338171324</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1818998974032927</v>
+        <v>-0.1818998974032951</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1809694267968064</v>
+        <v>-0.180969426796809</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1811975076256084</v>
+        <v>-0.1811975076256129</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1837403534986481</v>
+        <v>-0.1837403534986487</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1806391727170988</v>
+        <v>-0.1806391727171024</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2767646777040829</v>
+        <v>-0.2767646777040838</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1785131539410204</v>
+        <v>-0.1785131539410221</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1833400230259092</v>
+        <v>-0.1833400230259096</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1741594807588365</v>
+        <v>-0.1741594807588419</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1829630901405372</v>
+        <v>-0.1829630901405396</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1785140123634744</v>
+        <v>-0.1785140123634795</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1725463420705366</v>
+        <v>-0.1725463420705371</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7203783165648375</v>
+        <v>-0.7203783165648391</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8597931649953632</v>
+        <v>-0.859793164995363</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7214352044154126</v>
+        <v>-0.7214352044154153</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8380655074090195</v>
+        <v>-0.8380655074090183</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8050480788964814</v>
+        <v>-0.805048078896481</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.646114400519294</v>
+        <v>-0.646114400519295</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7330470281685924</v>
+        <v>-0.733047028168595</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7996835708393059</v>
+        <v>-0.7996835708393084</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7196849355784359</v>
+        <v>-0.7196849355784378</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7176913038908955</v>
+        <v>-0.7176913038908979</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6153347262651246</v>
+        <v>-0.6153347262651254</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5623448381287333</v>
+        <v>-0.5623448381287335</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7080846840323712</v>
+        <v>-0.7080846840323737</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7745837202882556</v>
+        <v>-0.7745837202882557</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7276108236167543</v>
+        <v>-0.7276108236167546</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.7702223111231735</v>
+        <v>-0.770222311123177</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7645579730299207</v>
+        <v>-0.7645579730299233</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6624930442941021</v>
+        <v>-0.6624930442941045</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7557821107984976</v>
+        <v>-0.7557821107984999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6837889665290678</v>
+        <v>-0.6837889665290675</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8696221990724359</v>
+        <v>-0.8696221990724372</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.674378804146373</v>
+        <v>-0.6743788041463726</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7365337586553631</v>
+        <v>-0.7365337586553619</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.7411565710130857</v>
+        <v>-0.7411565710130884</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7612611688169943</v>
+        <v>-0.761261168816995</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7109460591501594</v>
+        <v>-0.7109460591501614</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.5587887665247525</v>
+        <v>-0.558788766524751</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9048525452190742</v>
+        <v>-0.9048525452190789</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9016755919178234</v>
+        <v>-0.9016755919178281</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9050303493128768</v>
+        <v>-0.9050303493128767</v>
       </c>
       <c r="F7" t="n">
         <v>-0.9054353291247358</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9365536863949787</v>
+        <v>-0.93655368639498</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9368399716226631</v>
+        <v>-0.9368399716226646</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="M7" t="n">
         <v>-0.9001020256425537</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9038704892287153</v>
+        <v>-0.9038704892287186</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9399148218551684</v>
+        <v>-0.9399148218551718</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.940142902683971</v>
+        <v>-0.9401429026839738</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9057109453240695</v>
+        <v>-0.9057109453240745</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9395845677754604</v>
+        <v>-0.9395845677754623</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9385291350948807</v>
+        <v>-0.9385291350948795</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9374585489993831</v>
+        <v>-0.9374585489993832</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9422854180842722</v>
+        <v>-0.9422854180842712</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8961300725842583</v>
+        <v>-0.8961300725842613</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9049336819659598</v>
+        <v>-0.9049336819659619</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9004846041888965</v>
+        <v>-0.9004846041888968</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8945169338959593</v>
+        <v>-0.8945169338959592</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5336208512089599</v>
+        <v>-0.5336208512089584</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.766546748829503</v>
+        <v>-0.7665467488295029</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3629793505667784</v>
+        <v>-0.3629793505667776</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7334313477294089</v>
+        <v>-0.733431347729409</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7244567052039743</v>
+        <v>-0.7244567052039739</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1642585529027955</v>
+        <v>-0.1642585529027952</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.526614399730319</v>
+        <v>-0.5266143997303185</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6519246825604137</v>
+        <v>-0.6519246825604141</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3557125138375599</v>
+        <v>-0.355712513837559</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5260063586073511</v>
+        <v>-0.5260063586073516</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2479508440107822</v>
+        <v>-0.247950844010784</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1029466351301656</v>
+        <v>-0.1029466351301655</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5240775476558406</v>
+        <v>-0.5240775476558415</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5650647672919432</v>
+        <v>-0.5650647672919439</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3508690246508886</v>
+        <v>-0.3508690246508893</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7487093677080506</v>
+        <v>-0.74870936770805</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5987342255670834</v>
+        <v>-0.5987342255670839</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3190388266863624</v>
+        <v>-0.3190388266863626</v>
       </c>
       <c r="T2" t="n">
         <v>-0.571233022944019</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3551411722559485</v>
+        <v>-0.355141172255949</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6532305775493906</v>
+        <v>-0.6532305775493891</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2580182959148196</v>
+        <v>-0.2580182959148221</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2335750523268205</v>
+        <v>-0.2335750523268211</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.318762203657245</v>
+        <v>-0.3187622036572446</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5289924440608789</v>
+        <v>-0.5289924440608794</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4204802467523046</v>
+        <v>-0.4204802467523055</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.04592818741886234</v>
+        <v>-0.04592818741886156</v>
       </c>
     </row>
     <row r="3">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9317917972346202</v>
+        <v>-0.9317917972346185</v>
       </c>
       <c r="C3" t="n">
         <v>-0.9216078188049571</v>
@@ -2738,10 +2738,10 @@
         <v>-0.9286389715561262</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9314640981373977</v>
+        <v>-0.9314640981373976</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.918222795829952</v>
+        <v>-0.9182227958299504</v>
       </c>
       <c r="H3" t="n">
         <v>-0.9205531935219673</v>
@@ -2750,7 +2750,7 @@
         <v>-0.9205531935219673</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9214126686060687</v>
+        <v>-0.921412668606067</v>
       </c>
       <c r="K3" t="n">
         <v>-0.9205531935219673</v>
@@ -2759,19 +2759,19 @@
         <v>-0.9205531935219673</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9203983203244381</v>
+        <v>-0.920398320324438</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.929264991578442</v>
+        <v>-0.9292649915784413</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9268709138326368</v>
+        <v>-0.9268709138326339</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9274577601368135</v>
+        <v>-0.9274577601368127</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9340004393710342</v>
+        <v>-0.9340004393710317</v>
       </c>
       <c r="R3" t="n">
         <v>-0.9205531935219673</v>
@@ -2783,28 +2783,28 @@
         <v>-0.9205531935219673</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9260455065458055</v>
+        <v>-0.9260455065458004</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9257689959910974</v>
+        <v>-0.9257689959910961</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9205509848209008</v>
+        <v>-0.9205509848208995</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9329703990133537</v>
+        <v>-0.9329703990133518</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9093907104888401</v>
+        <v>-0.9093907104888425</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9320005600679473</v>
+        <v>-0.9320005600679481</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.9205531935219673</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.90754863365258</v>
+        <v>-0.9075486336525803</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04261465181096585</v>
+        <v>-0.0426146518109653</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1281836330910482</v>
+        <v>-0.1281836330910477</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0195821713994423</v>
+        <v>0.01958217139944248</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.116778793157184</v>
+        <v>-0.1167787931571827</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1130765044154942</v>
+        <v>-0.1130765044154929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09201356865054447</v>
+        <v>0.09201356865054451</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04006088252090881</v>
+        <v>-0.04006088252090936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0857350091448459</v>
+        <v>-0.08573500914484541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008645600938037191</v>
+        <v>0.008645600938039446</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03983925867156659</v>
+        <v>-0.03983925867156677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06150871130618429</v>
+        <v>0.06150871130618412</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1144594664534079</v>
+        <v>0.1144594664534075</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03913622972898278</v>
+        <v>-0.0391362297289827</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05407558999010891</v>
+        <v>-0.05407558999010953</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02399624298915825</v>
+        <v>0.02399624298915764</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1210118903780068</v>
+        <v>-0.1210118903780055</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.06634771216465872</v>
+        <v>-0.06634771216465843</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03559797637817198</v>
+        <v>0.03559797637817088</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05632384674397856</v>
+        <v>-0.05632384674397722</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02243909535320107</v>
+        <v>0.02243909535320125</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1745618640657833</v>
+        <v>-0.1745618640657784</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05783924330514977</v>
+        <v>0.05783924330514888</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06674851856591787</v>
+        <v>0.06674851856591728</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03569880222401375</v>
+        <v>0.03569880222401341</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.04092765175499185</v>
+        <v>-0.04092765175499198</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.001376230050568715</v>
+        <v>-0.001376230050568692</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1359474552400117</v>
+        <v>0.1359474552400132</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.187743286078013</v>
+        <v>-0.1877432860780115</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1847015722780892</v>
+        <v>-0.184701572278089</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1879296797983719</v>
+        <v>-0.1879296797983726</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1885282683361934</v>
+        <v>-0.1885282683361918</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1827975444012718</v>
+        <v>-0.1827975444012677</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1975454626884859</v>
+        <v>-0.1975454626884841</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.183492073797584</v>
+        <v>-0.1834920737975825</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1868222950875862</v>
+        <v>-0.1868222950875843</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1859496818619188</v>
+        <v>-0.1859496818619175</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.186163580448695</v>
+        <v>-0.1861635804486955</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1885483102015493</v>
+        <v>-0.1885483102015494</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1856488305982917</v>
+        <v>-0.1856488305982892</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2738989172800994</v>
+        <v>-0.2738989172801005</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1836461419494957</v>
+        <v>-0.1836461419494931</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1881728725865196</v>
+        <v>-0.1881728725865174</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1795783530060173</v>
+        <v>-0.1795783530060168</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1878193776793419</v>
+        <v>-0.1878193776793411</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1836469469950986</v>
+        <v>-0.1836469469950964</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1781030797540808</v>
+        <v>-0.1781030797540801</v>
       </c>
     </row>
     <row r="6">
@@ -2990,82 +2990,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7609804010450668</v>
+        <v>-0.7609804010450679</v>
       </c>
       <c r="C6" t="n">
         <v>-0.8465493823251486</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6987835778346594</v>
+        <v>-0.6987835778346597</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8351445423912831</v>
+        <v>-0.835144542391283</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8314422536495947</v>
+        <v>-0.8314422536495948</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.663275727247949</v>
+        <v>-0.6632757272479499</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7584266317550092</v>
+        <v>-0.7584266317550103</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8041007583789471</v>
+        <v>-0.8041007583789483</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.732036272589363</v>
+        <v>-0.732036272589361</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7582050079056676</v>
+        <v>-0.7582050079056682</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6568570379279176</v>
+        <v>-0.6568570379279184</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6039062827806909</v>
+        <v>-0.6039062827806906</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.757501978963084</v>
+        <v>-0.757501978963085</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8093648858886029</v>
+        <v>-0.8093648858886042</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.731293052909336</v>
+        <v>-0.7312930529093372</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.8393776396121082</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.784713461398758</v>
+        <v>-0.7847134613987597</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6827677728559298</v>
+        <v>-0.6827677728559306</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7746895959780772</v>
+        <v>-0.7746895959780782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7328502005452916</v>
+        <v>-0.7328502005452925</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.840354817731926</v>
+        <v>-0.8403548177319246</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6974500525933436</v>
+        <v>-0.6974500525933449</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6885407773325751</v>
+        <v>-0.6885407773325765</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.6826669470100876</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7592934009890924</v>
+        <v>-0.7592934009890938</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7197419792846707</v>
+        <v>-0.7197419792846715</v>
       </c>
       <c r="AB6" t="n">
         <v>-0.582418293994088</v>
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9061090353121125</v>
+        <v>-0.9061090353121135</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9030673215121886</v>
+        <v>-0.9030673215121885</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="E7" t="n">
         <v>-0.906295429032472</v>
@@ -3093,70 +3093,70 @@
         <v>-0.9068940175702939</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9380868402997645</v>
+        <v>-0.9380868402997617</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9382273362158859</v>
+        <v>-0.9382273362158861</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="M7" t="n">
         <v>-0.901857823031683</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9051880443216871</v>
+        <v>-0.9051880443216842</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9412389777604122</v>
+        <v>-0.9412389777604114</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9414528763471887</v>
+        <v>-0.9414528763471895</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9069140594356502</v>
+        <v>-0.9069140594356511</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9409381264967854</v>
+        <v>-0.9409381264967844</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9396918709462422</v>
+        <v>-0.9396918709462413</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9389354378479887</v>
+        <v>-0.9389354378479872</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.943462168485013</v>
+        <v>-0.9434621684850117</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8979441022401183</v>
+        <v>-0.8979441022401191</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9061851269134444</v>
+        <v>-0.9061851269134439</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9020126962291996</v>
+        <v>-0.9020126962291974</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8964688289881806</v>
+        <v>-0.8964688289881808</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5819311424936261</v>
+        <v>-0.581931142493625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7344880090019877</v>
+        <v>-0.7344880090019879</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5356708011316393</v>
+        <v>-0.535670801131637</v>
       </c>
       <c r="E2" t="n">
         <v>-0.797502450392949</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6860652336432798</v>
+        <v>-0.6860652336432794</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2757559722409698</v>
+        <v>-0.2757559722409676</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5722576387649271</v>
+        <v>-0.5722576387649264</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6459784140463507</v>
+        <v>-0.6459784140463503</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4091955217035507</v>
+        <v>-0.4091955217035511</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4547275831896034</v>
+        <v>-0.4547275831896021</v>
       </c>
       <c r="L2" t="n">
         <v>-0.3545288237061116</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2257242602877935</v>
+        <v>-0.2257242602877887</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5799423237618766</v>
+        <v>-0.5799423237618759</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6425490566402815</v>
+        <v>-0.6425490566402809</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3874339260847174</v>
+        <v>-0.3874339260847181</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6889088771255246</v>
+        <v>-0.6889088771255238</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6359085406666071</v>
+        <v>-0.6359085406666061</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3816628507771432</v>
+        <v>-0.3816628507771419</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6035850398203694</v>
+        <v>-0.6035850398203683</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3134682942654293</v>
+        <v>-0.3134682942654288</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4873566254331693</v>
+        <v>-0.48735662543317</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2603095103960741</v>
+        <v>-0.2603095103960729</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2051758446900525</v>
+        <v>-0.2051758446900522</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.06585688230954682</v>
+        <v>-0.06585688230954471</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5772056928362685</v>
+        <v>-0.5772056928362672</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3922691409334481</v>
+        <v>-0.392269140933447</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1336208488320138</v>
+        <v>-0.1336208488320137</v>
       </c>
     </row>
     <row r="3">
@@ -3410,82 +3410,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9334909857672778</v>
+        <v>-0.9334909857672777</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9235274354290787</v>
+        <v>-0.9235274354290786</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9304375463571184</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9328657711488803</v>
+        <v>-0.9328657711488801</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9205178507435859</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9233833616237959</v>
+        <v>-0.9233833616237964</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9227086403235706</v>
+        <v>-0.9227086403235669</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9310751417429689</v>
+        <v>-0.9310751417429691</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.92878619704225</v>
+        <v>-0.9287861970422508</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9293472726967807</v>
+        <v>-0.929347272696781</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9356026380402691</v>
+        <v>-0.9356026380402682</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.928022907268661</v>
+        <v>-0.9280229072686597</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9272966813801746</v>
+        <v>-0.927296681380175</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9227438001135707</v>
+        <v>-0.9227438001135695</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9346178306657589</v>
+        <v>-0.9346178306657591</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9121178731271703</v>
+        <v>-0.912117873127169</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9336905810319015</v>
+        <v>-0.9336905810319013</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9227459118231464</v>
+        <v>-0.9227459118231455</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.9103194670436224</v>
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06791391030980096</v>
+        <v>-0.06791391030980114</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1240157641676139</v>
+        <v>-0.1240157641676145</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05105255909971089</v>
+        <v>-0.05105255909971081</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1477392056665207</v>
+        <v>-0.1477392056665208</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1065360517896401</v>
+        <v>-0.1065360517896405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0436833439569228</v>
+        <v>0.04368334395692329</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.06438803179270725</v>
+        <v>-0.0643880317927069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09125838870973745</v>
+        <v>-0.09125838870973703</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01570519394682733</v>
+        <v>-0.01570519394682773</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.02154970664309336</v>
+        <v>-0.02154970664309391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01497156459540201</v>
+        <v>0.01497156459540303</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06194300193746269</v>
+        <v>0.06194300193746478</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06718900923596768</v>
+        <v>-0.06718900923596789</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09000842820477366</v>
+        <v>-0.0900084282047738</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00297804116962058</v>
+        <v>0.002978041169619148</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1069060383871463</v>
+        <v>-0.1069060383871464</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.08758803810924397</v>
+        <v>-0.08758803810924366</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005081530351842892</v>
+        <v>0.005081530351842866</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0758065016125016</v>
+        <v>-0.07580650161250164</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02993764541945246</v>
+        <v>0.02993764541945229</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1034732429363788</v>
+        <v>-0.1034732429363749</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04931339791787506</v>
+        <v>0.04931339791787553</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0694089716555288</v>
+        <v>0.0694089716555302</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1201890974773712</v>
+        <v>0.1201890974773717</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.06619153939872749</v>
+        <v>-0.06619153939872724</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001215662135216344</v>
+        <v>0.001215662135216951</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09625401369759649</v>
+        <v>0.09625401369759644</v>
       </c>
     </row>
     <row r="5">
@@ -3589,82 +3589,82 @@
         <v>-0.1960533449589444</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1929184152872697</v>
+        <v>-0.1929184152872703</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1961924871427518</v>
+        <v>-0.196192487142752</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1964919496322024</v>
+        <v>-0.1964919496322027</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1913247895810501</v>
+        <v>-0.1913247895810505</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2031206236992993</v>
+        <v>-0.2031206236992998</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1920996201817761</v>
+        <v>-0.1920996201817731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1951727981803564</v>
+        <v>-0.1951727981803555</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1943385047150893</v>
+        <v>-0.1943385047150902</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1945430102026851</v>
+        <v>-0.1945430102026839</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1968230174161767</v>
+        <v>-0.1968230174161762</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1940602945556157</v>
+        <v>-0.1940602945556166</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.263826227292104</v>
+        <v>-0.2638262272921005</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1921361219879938</v>
+        <v>-0.1921361219879933</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1964640666923628</v>
+        <v>-0.1964640666923604</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1882630963773833</v>
+        <v>-0.1882630963773839</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1961260950891335</v>
+        <v>-0.1961260950891342</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1921368916813373</v>
+        <v>-0.1921368916813374</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1868435121848878</v>
+        <v>-0.1868435121848873</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7791966558076616</v>
+        <v>-0.7791966558076613</v>
       </c>
       <c r="C6" t="n">
         <v>-0.8352985096654726</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7623353045975715</v>
+        <v>-0.7623353045975708</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8590219511643798</v>
+        <v>-0.8590219511643797</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8178187972874978</v>
+        <v>-0.817818797287498</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7045014560477434</v>
+        <v>-0.7045014560477436</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7756707772905665</v>
+        <v>-0.7756707772905662</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8025411342075964</v>
+        <v>-0.8025411342075959</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7519761264391736</v>
+        <v>-0.7519761264391737</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7328324521409528</v>
+        <v>-0.7328324521409519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.696311180902456</v>
+        <v>-0.6963111809024567</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6493397435603975</v>
+        <v>-0.6493397435603983</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7784717547338277</v>
+        <v>-0.7784717547338269</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8381932282094413</v>
+        <v>-0.8381932282094401</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7452067588350478</v>
+        <v>-0.7452067588350475</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.818188783885006</v>
+        <v>-0.8181887838850054</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7988707836071032</v>
+        <v>-0.7988707836071025</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7062012151460139</v>
+        <v>-0.7062012151460155</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7870892471103592</v>
+        <v>-0.7870892471103593</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7182471545852167</v>
+        <v>-0.7182471545852157</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7801282695279587</v>
+        <v>-0.7801282695279588</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6988714020867938</v>
+        <v>-0.6988714020867928</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6787758283491382</v>
+        <v>-0.6787758283491357</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5910936480204861</v>
+        <v>-0.5910936480204856</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7774742848965847</v>
+        <v>-0.7774742848965855</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7100670833626413</v>
+        <v>-0.7100670833626408</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.6150287318002609</v>
+        <v>-0.6150287318002607</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9073360904568022</v>
+        <v>-0.9073360904568025</v>
       </c>
       <c r="C7" t="n">
         <v>-0.9042011607851284</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9074752326406108</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9077746951300601</v>
+        <v>-0.9077746951300604</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9395095895857176</v>
+        <v>-0.9395095895857183</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9393915561916472</v>
+        <v>-0.9393915561916468</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9033823656796349</v>
+        <v>-0.9033823656796366</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9064555436782153</v>
+        <v>-0.9064555436782151</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9425233047197572</v>
+        <v>-0.9425233047197574</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9427278102073513</v>
+        <v>-0.9427278102073506</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.908105762914035</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9422450945602857</v>
+        <v>-0.9422450945602843</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9404812538836834</v>
+        <v>-0.9404812538836831</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9403209219926598</v>
+        <v>-0.94032092199266</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9446488666970277</v>
+        <v>-0.944648866697027</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8995458418752418</v>
+        <v>-0.899545841875243</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9074088405869934</v>
+        <v>-0.9074088405869921</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9034196371791937</v>
+        <v>-0.9034196371791949</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8981262576827452</v>
+        <v>-0.8981262576827453</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.8834936170728398</v>
+        <v>-0.88349361707284</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9144464336312651</v>
+        <v>-0.9144464336312652</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7758310156443773</v>
+        <v>-0.7758310156443775</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9593001775781538</v>
+        <v>-0.959300177578154</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9548991693187153</v>
+        <v>-0.9548991693187157</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7144281567817367</v>
+        <v>-0.7144281567817365</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8674971411220856</v>
+        <v>-0.8674971411220855</v>
       </c>
       <c r="I2" t="n">
         <v>-0.8696529399178176</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7846929722320237</v>
+        <v>-0.7846929722320239</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7711850831698513</v>
+        <v>-0.7711850831698511</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9184698318390755</v>
+        <v>-0.9184698318390763</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6779088643487828</v>
+        <v>-0.6779088643487829</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8395077850468134</v>
+        <v>-0.8395077850468147</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.910747692635942</v>
+        <v>-0.9107476926359415</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8815615382904212</v>
+        <v>-0.8815615382904205</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8904830476744593</v>
+        <v>-0.8904830476744601</v>
       </c>
       <c r="R2" t="n">
         <v>-1.170684219841774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8393777210054669</v>
+        <v>-0.8393777210054674</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9013673712181984</v>
+        <v>-0.901367371218198</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6057071005518861</v>
+        <v>-0.6057071005518857</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8901712459419296</v>
+        <v>-0.8901712459419302</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3247327531531557</v>
+        <v>-0.3247327531531547</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6541076965907296</v>
+        <v>-0.6541076965907295</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8213759378044725</v>
+        <v>-0.8213759378044769</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.8789203775478557</v>
+        <v>-0.8789203775478556</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.6235069036169327</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.7050717892002445</v>
+        <v>-0.7050717892002444</v>
       </c>
     </row>
     <row r="3">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9446042123521053</v>
+        <v>-0.9446042123521048</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9364966743418766</v>
+        <v>-0.9364966743418768</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9416608036516321</v>
@@ -4109,70 +4109,70 @@
         <v>-0.9439301755189646</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9347477395449076</v>
+        <v>-0.9347477395449062</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="J3" t="n">
         <v>-0.9367649668967004</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="M3" t="n">
         <v>-0.9363598567986953</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9427687499993574</v>
+        <v>-0.9427687499993571</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9410297007129513</v>
+        <v>-0.9410297007129507</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9414559837142059</v>
+        <v>-0.9414559837142051</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9462085618923817</v>
+        <v>-0.9462085618923813</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9404861737865402</v>
+        <v>-0.9404861737865399</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9395600058534014</v>
+        <v>-0.9395600058534016</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.93643892747947</v>
+        <v>-0.9364389274794694</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9454603443570172</v>
+        <v>-0.9454603443570169</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9284280233985618</v>
+        <v>-0.9284280233985619</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9447558569080893</v>
+        <v>-0.9447558569080891</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9364405318733099</v>
+        <v>-0.9364405318733092</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9273068557820645</v>
+        <v>-0.9273068557820646</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.215012886278048</v>
+        <v>-0.2150128862780478</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2263305036453037</v>
+        <v>-0.2263305036453036</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1757711322954689</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2431985133366875</v>
+        <v>-0.2431985133366877</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2414192609148019</v>
+        <v>-0.2414192609148012</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1533905112688078</v>
+        <v>-0.1533905112688082</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2091823586341021</v>
+        <v>-0.2091823586341009</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2099681219804797</v>
+        <v>-0.2099681219804778</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1897738412833693</v>
+        <v>-0.1897738412833683</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1740777444637955</v>
+        <v>-0.1740777444637953</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.227761305848891</v>
+        <v>-0.2277613058488908</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.140028388050938</v>
+        <v>-0.1400283880509382</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1989805670122792</v>
+        <v>-0.1989805670122793</v>
       </c>
       <c r="O4" t="n">
         <v>-0.2249466767872859</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2143086662494696</v>
+        <v>-0.2143086662494692</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175604516583009</v>
+        <v>-0.2175604516583001</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3196904886250041</v>
+        <v>-0.3196904886250035</v>
       </c>
       <c r="S4" t="n">
         <v>-0.1989331601964968</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2215276597798133</v>
+        <v>-0.2215276597798131</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1137629629401265</v>
+        <v>-0.1137629629401266</v>
       </c>
       <c r="V4" t="n">
         <v>-0.288465058744746</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.01135111268065361</v>
+        <v>-0.01135111268065367</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1314044118477912</v>
+        <v>-0.1314044118477909</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1923717216073466</v>
+        <v>-0.1923717216073473</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2133459941728808</v>
+        <v>-0.2133459941728802</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.1202507821414951</v>
+        <v>-0.120250782141495</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.1495950864816319</v>
+        <v>-0.1495950864816316</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.237286980660502</v>
+        <v>-0.2372869806605003</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2343675574573219</v>
+        <v>-0.2343675574573211</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2367691686724576</v>
+        <v>-0.236769168672457</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2374211914792208</v>
+        <v>-0.2374211914792201</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2336944120628246</v>
+        <v>-0.2336944120628234</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2452022976191265</v>
+        <v>-0.2452022976191263</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2342307399141524</v>
+        <v>-0.2342307399141519</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2366179761860107</v>
+        <v>-0.2366179761860102</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2359841131420634</v>
+        <v>-0.2359841131420626</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2361394882903541</v>
+        <v>-0.2361394882903537</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2378717472287072</v>
+        <v>-0.2378717472287068</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2357860039598026</v>
+        <v>-0.2357860039598031</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3064666817803771</v>
+        <v>-0.3064666817803776</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2343108302060405</v>
+        <v>-0.2343108302060407</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2375990307230818</v>
+        <v>-0.2375990307230822</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2313909497373361</v>
+        <v>-0.231390949737335</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2373422533204555</v>
+        <v>-0.2373422533204535</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2343114149887569</v>
+        <v>-0.2343114149887567</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2305971586347995</v>
+        <v>-0.2305971586347993</v>
       </c>
     </row>
     <row r="6">
@@ -4364,67 +4364,67 @@
         <v>-0.904987439978241</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8544280686284053</v>
+        <v>-0.8544280686284056</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9218554496696256</v>
+        <v>-0.9218554496696258</v>
       </c>
       <c r="F6" t="n">
         <v>-0.9200761972477395</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.868873007731348</v>
+        <v>-0.8688730077313487</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8878392949670396</v>
+        <v>-0.8878392949670384</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8886250583134166</v>
+        <v>-0.8886250583134154</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.893126302095416</v>
+        <v>-0.8931263020954155</v>
       </c>
       <c r="K6" t="n">
         <v>-0.8527346807967341</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9064182421818285</v>
+        <v>-0.9064182421818291</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8186853243838761</v>
+        <v>-0.8186853243838762</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8776375033452158</v>
+        <v>-0.8776375033452163</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9404291732498266</v>
+        <v>-0.9404291732498263</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9297911627120116</v>
+        <v>-0.9297911627120115</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8962173879912378</v>
+        <v>-0.8962173879912377</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.9983474249579409</v>
+        <v>-0.9983474249579408</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8775900965294349</v>
+        <v>-0.8775900965294342</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9001845961127509</v>
+        <v>-0.9001845961127508</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8292454594026661</v>
+        <v>-0.8292454594026669</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9309559510401326</v>
+        <v>-0.930955951040133</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7268336091431938</v>
+        <v>-0.7268336091431942</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8468869083103312</v>
+        <v>-0.8468869083103309</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.8710286579402837</v>
@@ -4433,10 +4433,10 @@
         <v>-0.8920029305058186</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7989077184744318</v>
+        <v>-0.7989077184744321</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.8282520228145706</v>
+        <v>-0.8282520228145707</v>
       </c>
     </row>
     <row r="7">
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9159439169934378</v>
+        <v>-0.9159439169934369</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9130244937902597</v>
+        <v>-0.91302449379026</v>
       </c>
       <c r="D7" t="n">
         <v>-0.912968351321693</v>
@@ -4461,7 +4461,7 @@
         <v>-0.9160781278121586</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9491769085253653</v>
+        <v>-0.9491769085253643</v>
       </c>
       <c r="H7" t="n">
         <v>-0.912968351321693</v>
@@ -4470,7 +4470,7 @@
         <v>-0.912968351321693</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.948554758431172</v>
+        <v>-0.9485547584311721</v>
       </c>
       <c r="K7" t="n">
         <v>-0.912968351321693</v>
@@ -4482,16 +4482,16 @@
         <v>-0.9128876762470908</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9152749125189484</v>
+        <v>-0.9152749125189487</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9514666096046047</v>
+        <v>-0.9514666096046039</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9516219847528941</v>
+        <v>-0.9516219847528937</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9165286835616452</v>
+        <v>-0.9165286835616447</v>
       </c>
       <c r="R7" t="n">
         <v>-0.912968351321693</v>
@@ -4503,28 +4503,28 @@
         <v>-0.912968351321693</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9512685004223435</v>
+        <v>-0.9512685004223437</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9489575740757648</v>
+        <v>-0.9489575740757649</v>
       </c>
       <c r="W7" t="n">
         <v>-0.9497933266685816</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.953081527185622</v>
+        <v>-0.9530815271856227</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.9100478860702724</v>
+        <v>-0.9100478860702715</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.915999189653394</v>
+        <v>-0.9159991896533934</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.912968351321693</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.9092540949677381</v>
+        <v>-0.909254094967738</v>
       </c>
     </row>
   </sheetData>
@@ -4690,13 +4690,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.128896237531905</v>
+        <v>-1.128896237531907</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.9571418620328972</v>
+        <v>-0.9571418620328963</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9032679556226431</v>
+        <v>-0.9032679556226444</v>
       </c>
       <c r="E2" t="n">
         <v>-1.272236036360499</v>
@@ -4705,70 +4705,70 @@
         <v>-1.220451678011174</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7856839168330745</v>
+        <v>-0.7856839168330774</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9410362710541729</v>
+        <v>-0.9410362710541742</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9979416550481115</v>
+        <v>-0.9979416550481125</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9070031580780612</v>
+        <v>-0.9070031580780624</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9977947726658651</v>
+        <v>-0.9977947726658659</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.283893895208309</v>
+        <v>-1.28389389520831</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9716412270246187</v>
+        <v>-0.971641227024619</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8370556420852573</v>
+        <v>-0.8370556420852583</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9646922215759794</v>
+        <v>-0.9646922215759806</v>
       </c>
       <c r="P2" t="n">
         <v>-1.131383809208844</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9421277366367262</v>
+        <v>-0.9421277366367276</v>
       </c>
       <c r="R2" t="n">
         <v>-1.592916888495719</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.038307684627601</v>
+        <v>-1.038307684627604</v>
       </c>
       <c r="T2" t="n">
         <v>-1.058888608846954</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9210173818606155</v>
+        <v>-0.9210173818606171</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8960286275374425</v>
+        <v>-0.8960286275374441</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6316611610299026</v>
+        <v>-0.6316611610299044</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2538879983424193</v>
+        <v>-0.2538879983424202</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.7358005556192512</v>
+        <v>-0.7358005556192518</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.9393330692799924</v>
+        <v>-0.9393330692799942</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4429684955586312</v>
+        <v>-0.4429684955586328</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.9576677842951431</v>
+        <v>-0.9576677842951432</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9496215165751885</v>
+        <v>-0.9496215165751875</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.942800133148064</v>
+        <v>-0.942800133148066</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9474821170895694</v>
+        <v>-0.9474821170895695</v>
       </c>
       <c r="F3" t="n">
         <v>-0.9496325355393452</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9416592575473707</v>
+        <v>-0.9416592575473703</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9431575393255505</v>
+        <v>-0.9431575393255515</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9432989435884104</v>
+        <v>-0.9432989435884105</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.948138792786957</v>
+        <v>-0.9481387927869571</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.946733953432097</v>
+        <v>-0.9467339534320993</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9470783135037648</v>
+        <v>-0.9470783135037651</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9509175427371143</v>
+        <v>-0.9509175427371134</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9463311009119791</v>
+        <v>-0.9463311009119794</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.94521987948287</v>
+        <v>-0.9452198794828712</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9430254335234423</v>
+        <v>-0.943025433523444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9503131174047074</v>
+        <v>-0.9503131174047089</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9366160235760533</v>
+        <v>-0.9366160235760552</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9497440181294998</v>
+        <v>-0.9497440181295008</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9430267295898952</v>
+        <v>-0.9430267295898982</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9359361198674976</v>
+        <v>-0.9359361198674978</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3162698524016473</v>
+        <v>-0.3162698524016482</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2535233946743476</v>
+        <v>-0.2535233946743495</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2340309931067731</v>
+        <v>-0.2340309931067739</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3691153587129536</v>
+        <v>-0.3691153587129533</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3503006569171265</v>
+        <v>-0.350300656917127</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1911729917094701</v>
+        <v>-0.1911729917094703</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.247797100583614</v>
+        <v>-0.2477971005836152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2685384448326477</v>
+        <v>-0.2685384448326495</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2451785896565202</v>
+        <v>-0.2451785896565199</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2684849079290991</v>
+        <v>-0.2684849079291005</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3727646785503073</v>
+        <v>-0.3727646785503082</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2591252428458533</v>
+        <v>-0.2591252428458528</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2098973823266353</v>
+        <v>-0.2098973823266372</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2564194167666181</v>
+        <v>-0.2564194167666193</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3171765430673494</v>
+        <v>-0.3171765430673496</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2481949269718186</v>
+        <v>-0.248194926971816</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4853999308723755</v>
+        <v>-0.4853999308723758</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2832513886125226</v>
+        <v>-0.2832513886125244</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.290752893817062</v>
+        <v>-0.2907528938170623</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2405004505462264</v>
+        <v>-0.2405004505462279</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2963167376386452</v>
+        <v>-0.2963167376386474</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1350335058457252</v>
+        <v>-0.1350335058457266</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002660375917421312</v>
+        <v>0.002660375917420721</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1729910923070318</v>
+        <v>-0.1729910923070324</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2471763035369312</v>
+        <v>-0.2471763035369326</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.06625724502259223</v>
+        <v>-0.06625724502259321</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2537308435169073</v>
+        <v>-0.2537308435169068</v>
       </c>
     </row>
     <row r="5">
@@ -4954,82 +4954,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2509263217629811</v>
+        <v>-0.2509263217629861</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.248296002904908</v>
+        <v>-0.2482960029049111</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2507463685917539</v>
+        <v>-0.2507463685917534</v>
       </c>
       <c r="F5" t="n">
         <v>-0.251590259605074</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2480241718449081</v>
+        <v>-0.2480241718449087</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2583564370750512</v>
+        <v>-0.2583564370750517</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2487948133452492</v>
+        <v>-0.2487948133452488</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2503858863531916</v>
+        <v>-0.2503858863531915</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2498738389048045</v>
+        <v>-0.2498738389048039</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2499993541072469</v>
+        <v>-0.2499993541072465</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2513987080802957</v>
+        <v>-0.2513987080802965</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2497270038917531</v>
+        <v>-0.2497270038917525</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3142463713399118</v>
+        <v>-0.3142463713399136</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2485221269457375</v>
+        <v>-0.2485221269457381</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2511784021441534</v>
+        <v>-0.2511784021441567</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2461859722830069</v>
+        <v>-0.2461859722830086</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2509709721410427</v>
+        <v>-0.2509709721410424</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2485225993467419</v>
+        <v>-0.2485225993467433</v>
       </c>
       <c r="AB5" t="n">
         <v>-0.2458099070191185</v>
@@ -5042,13 +5042,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9848364104120934</v>
+        <v>-0.9848364104120946</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9220899526847941</v>
+        <v>-0.922089952684795</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.902597551117219</v>
+        <v>-0.9025975511172204</v>
       </c>
       <c r="E6" t="n">
         <v>-1.0376819167234</v>
@@ -5057,70 +5057,70 @@
         <v>-1.018867214927573</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8964642533313859</v>
+        <v>-0.8964642533313877</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9163636585940607</v>
+        <v>-0.916363658594062</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9371050028430957</v>
+        <v>-0.9371050028430965</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9392066158406401</v>
+        <v>-0.9392066158406406</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9370514659395466</v>
+        <v>-0.9370514659395478</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.041331236560754</v>
+        <v>-1.041331236560755</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9276918008562992</v>
+        <v>-0.9276918008562993</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8784639403370823</v>
+        <v>-0.8784639403370827</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9617106783885339</v>
+        <v>-0.9617106783885351</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.022467804689266</v>
+        <v>-1.022467804689268</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9167614849822652</v>
+        <v>-0.9167614849822635</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.15396648888282</v>
+        <v>-1.153966488882822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9518179466229699</v>
+        <v>-0.9518179466229706</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9593194518275091</v>
+        <v>-0.9593194518275098</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9457917121681449</v>
+        <v>-0.9457917121681457</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9343814843240693</v>
+        <v>-0.9343814843240692</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.8403247674676417</v>
+        <v>-0.8403247674676431</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7026308857044965</v>
+        <v>-0.7026308857044976</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.8415576503174774</v>
+        <v>-0.8415576503174788</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.9157428615473769</v>
+        <v>-0.9157428615473779</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7348238030330386</v>
+        <v>-0.7348238030330403</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.9222974015273542</v>
+        <v>-0.9222974015273543</v>
       </c>
     </row>
     <row r="7">
@@ -5130,43 +5130,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9194928797734281</v>
+        <v>-0.9194928797734331</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9168625609153555</v>
+        <v>-0.9168625609153581</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9193129266022</v>
+        <v>-0.9193129266022001</v>
       </c>
       <c r="F7" t="n">
         <v>-0.92015681761552</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9533154334668247</v>
+        <v>-0.953315433466826</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9523844632591711</v>
+        <v>-0.9523844632591725</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9173613713556963</v>
+        <v>-0.9173613713556964</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9189524443636393</v>
+        <v>-0.91895244436364</v>
       </c>
       <c r="O7" t="n">
         <v>-0.9551651005267201</v>
@@ -5175,40 +5175,40 @@
         <v>-0.9552906157291632</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9199652660907432</v>
+        <v>-0.9199652660907431</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9550182655136707</v>
+        <v>-0.9550182655136704</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9523111180253333</v>
+        <v>-0.952311118025334</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9538133885676546</v>
+        <v>-0.9538133885676559</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9564696637660715</v>
+        <v>-0.9564696637660736</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.914752530293453</v>
+        <v>-0.9147525302934546</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9195375301514881</v>
+        <v>-0.919537530151489</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9170891573571879</v>
+        <v>-0.9170891573571887</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.914376465029565</v>
+        <v>-0.9143764650295652</v>
       </c>
     </row>
   </sheetData>
@@ -5380,7 +5380,7 @@
         <v>-1.065288675672012</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.004287175429888</v>
+        <v>-1.00428717542989</v>
       </c>
       <c r="E2" t="n">
         <v>-1.320939728783926</v>
@@ -5389,67 +5389,67 @@
         <v>-1.179677089315927</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8243724932841632</v>
+        <v>-0.8243724932841648</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9119591606231742</v>
+        <v>-0.9119591606231745</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9508452036368341</v>
+        <v>-0.9508452036368353</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9401854869529777</v>
+        <v>-0.9401854869529768</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9770116799616454</v>
+        <v>-0.9770116799616467</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.359144169567047</v>
+        <v>-1.359144169567049</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9417905871673691</v>
+        <v>-0.9417905871673683</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8133675458244437</v>
+        <v>-0.8133675458244448</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.089655816209325</v>
+        <v>-1.089655816209326</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.183392425902032</v>
+        <v>-1.183392425902034</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9357400144301471</v>
+        <v>-0.9357400144301488</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.57630322765922</v>
+        <v>-1.576303227659221</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.11108313858317</v>
+        <v>-1.111083138583173</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.026780720578011</v>
+        <v>-1.026780720578012</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9202596525672935</v>
+        <v>-0.920259652567295</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8707278305346213</v>
+        <v>-0.8707278305346212</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6739009125623172</v>
+        <v>-0.6739009125623188</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03463614772060357</v>
+        <v>-0.03463614772060345</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.801748821360201</v>
+        <v>-0.8017488213602022</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.052673155037177</v>
+        <v>-1.052673155037179</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3655172887255481</v>
+        <v>-0.3655172887255483</v>
       </c>
       <c r="AB2" t="n">
         <v>-0.9348039583674469</v>
@@ -5462,82 +5462,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9518272124626044</v>
+        <v>-0.951827212462605</v>
       </c>
       <c r="C3" t="n">
         <v>-0.9455527301102116</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9496916280663407</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9514498649751125</v>
+        <v>-0.9514498649751126</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9445572768893419</v>
+        <v>-0.944557276889343</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9457488640581977</v>
+        <v>-0.9457488640581975</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9456674042984921</v>
+        <v>-0.9456674042984915</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9504734124441094</v>
+        <v>-0.9504734124441111</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.949190724757707</v>
+        <v>-0.9491907247577109</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9495051425039928</v>
+        <v>-0.9495051425039942</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9530105483314593</v>
+        <v>-0.953010548331461</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9488557918372705</v>
+        <v>-0.9488557918372711</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9474588252199908</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9458046629980802</v>
+        <v>-0.9458046629980831</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9524586781618802</v>
+        <v>-0.9524586781618806</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.940008822774318</v>
+        <v>-0.9400088227743207</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9519390624296192</v>
+        <v>-0.95193906242962</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9458058463737224</v>
+        <v>-0.9458058463737236</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.9388967280519029</v>
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3775664390896594</v>
+        <v>-0.3775664390896606</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2993001233686283</v>
+        <v>-0.2993001233686284</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2772266512038567</v>
+        <v>-0.2772266512038598</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3930746708368196</v>
+        <v>-0.3930746708368192</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3415105536926806</v>
+        <v>-0.3415105536926814</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2116498622266006</v>
+        <v>-0.211649862226603</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2435741739770976</v>
+        <v>-0.2435741739770995</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2577476800326045</v>
+        <v>-0.2577476800326064</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2627140848404009</v>
+        <v>-0.2627140848404021</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2672850533907206</v>
+        <v>-0.2672850533907238</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4065678586256462</v>
+        <v>-0.4065678586256481</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.254359397089666</v>
+        <v>-0.2543593970896655</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.207638688104151</v>
+        <v>-0.2076386881041527</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3083425183187717</v>
+        <v>-0.3083425183187727</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.342508411840918</v>
+        <v>-0.3425084118409196</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2522420159408533</v>
+        <v>-0.2522420159408553</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4857197852898381</v>
+        <v>-0.4857197852898398</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3161525257117136</v>
+        <v>-0.3161525257117161</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2854252842778037</v>
+        <v>-0.2854252842778059</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2465996058214294</v>
+        <v>-0.2465996058214325</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.287770774754155</v>
+        <v>-0.2877707747541543</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1568047379799993</v>
+        <v>-0.1568047379800002</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07619976217894529</v>
+        <v>0.07619976217894206</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.203403799470886</v>
+        <v>-0.2034037994708884</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2948627725938552</v>
+        <v>-0.2948627725938572</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.0444025283148352</v>
+        <v>-0.04440252831483775</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2515072633854235</v>
+        <v>-0.2515072633854238</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2581056107182662</v>
+        <v>-0.258105610718268</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.255657777221811</v>
+        <v>-0.2556577772218107</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2577590975405556</v>
+        <v>-0.257759097540556</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2583244103998281</v>
+        <v>-0.2583244103998286</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2554558045697081</v>
+        <v>-0.2554558045697077</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.264741870466781</v>
+        <v>-0.2647418704667823</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2557724514100753</v>
+        <v>-0.2557724514100747</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2576121665086512</v>
+        <v>-0.2576121665086535</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2571446419090368</v>
+        <v>-0.2571446419090379</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2572592434854758</v>
+        <v>-0.2572592434854779</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2585369227470344</v>
+        <v>-0.2585369227470372</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2570225627925171</v>
+        <v>-0.2570225627925192</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3157383212961414</v>
+        <v>-0.3157383212961404</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2559104621587964</v>
+        <v>-0.2559104621587977</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2583357725506089</v>
+        <v>-0.258335772550612</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2537979464554264</v>
+        <v>-0.2537979464554278</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.258146378717837</v>
+        <v>-0.258146378717838</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.255910893485322</v>
+        <v>-0.2559108934853231</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2529990298756771</v>
+        <v>-0.2529990298756774</v>
       </c>
     </row>
     <row r="6">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.040627170197741</v>
+        <v>-1.040627170197744</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9623608544767112</v>
+        <v>-0.9623608544767113</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9402873823119393</v>
+        <v>-0.9402873823119421</v>
       </c>
       <c r="E6" t="n">
         <v>-1.056135401944903</v>
@@ -5741,67 +5741,67 @@
         <v>-1.004571284800763</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9113939986033954</v>
+        <v>-0.9113939986033968</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9066349050851787</v>
+        <v>-0.9066349050851813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.920808411140687</v>
+        <v>-0.9208084111406899</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9520115810874099</v>
+        <v>-0.9520115810874111</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9303457844988028</v>
+        <v>-0.9303457844988069</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.069628589733728</v>
+        <v>-1.069628589733731</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9174201281977497</v>
+        <v>-0.9174201281977489</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8706994192122333</v>
+        <v>-0.8706994192122364</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.008086654695564</v>
+        <v>-1.008086654695566</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.042252548217712</v>
+        <v>-1.042252548217714</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.915302747048937</v>
+        <v>-0.9153027470489394</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.148780516397921</v>
+        <v>-1.148780516397924</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9792132568197962</v>
+        <v>-0.9792132568198001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9484860153858875</v>
+        <v>-0.9484860153858899</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9463437421982249</v>
+        <v>-0.9463437421982274</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9257285574339943</v>
+        <v>-0.9257285574339944</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.8565488743567914</v>
+        <v>-0.8565488743567929</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6235443741978484</v>
+        <v>-0.6235443741978507</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.866464530578968</v>
+        <v>-0.8664645305789713</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.9579235037019382</v>
+        <v>-0.9579235037019405</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7074632594229165</v>
+        <v>-0.70746325942292</v>
       </c>
       <c r="AB6" t="n">
         <v>-0.9145679944935045</v>
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9211663418263518</v>
+        <v>-0.9211663418263522</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.918718508329894</v>
+        <v>-0.9187185083298942</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9208198286486393</v>
@@ -5829,67 +5829,67 @@
         <v>-0.9213851415079113</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9551999409465017</v>
+        <v>-0.9551999409465016</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9540393667137906</v>
+        <v>-0.9540393667137914</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9188331825181589</v>
+        <v>-0.918833182518158</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9206728976167325</v>
+        <v>-0.9206728976167357</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9568887782858303</v>
+        <v>-0.9568887782858305</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9570033798622695</v>
+        <v>-0.9570033798622712</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9215976538551185</v>
+        <v>-0.9215976538551197</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9567666991693107</v>
+        <v>-0.9567666991693126</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9536961039759809</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9556545985355904</v>
+        <v>-0.9556545985355913</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9580799089274026</v>
+        <v>-0.9580799089274057</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.9168586775635086</v>
+        <v>-0.9168586775635116</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9212071098259209</v>
+        <v>-0.9212071098259214</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9189716245934052</v>
+        <v>-0.9189716245934059</v>
       </c>
       <c r="AB7" t="n">
         <v>-0.9160597609837607</v>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6424641867739341</v>
+        <v>-0.6424641867739278</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8801613386565498</v>
+        <v>-0.8801613386565487</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5929448933830638</v>
+        <v>-0.5929448933830568</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8526251573826229</v>
+        <v>-0.8526251573826185</v>
       </c>
       <c r="F2" t="n">
         <v>-0.8465681894794653</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1679633372304592</v>
+        <v>-0.1679633372304521</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5426626971877629</v>
+        <v>-0.5426626971877574</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8067773735656979</v>
+        <v>-0.8067773735656927</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4430779411152584</v>
+        <v>-0.4430779411152561</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6562558260443089</v>
+        <v>-0.6562558260443031</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3098799251288581</v>
+        <v>-0.3098799251288527</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07226027791761022</v>
+        <v>-0.07226027791761014</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5769859675813009</v>
+        <v>-0.5769859675812959</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6694545845367489</v>
+        <v>-0.669454584536743</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5652052630262245</v>
+        <v>-0.5652052630262208</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7516426347910656</v>
+        <v>-0.75164263479106</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.9032926419341203</v>
+        <v>-0.9032926419341256</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.556846721039297</v>
+        <v>-0.5568467210392913</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7688790734833116</v>
+        <v>-0.7688790734833058</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3649418953426584</v>
+        <v>-0.3649418953426515</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7683379690111504</v>
+        <v>-0.7683379690111506</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3078848800157835</v>
+        <v>-0.3078848800157761</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4355657559602632</v>
+        <v>-0.4355657559602558</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.5011882191006236</v>
+        <v>-0.5011882191006182</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.6878591518332515</v>
+        <v>-0.6878591518332468</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4527169242199787</v>
+        <v>-0.4527169242199734</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1088191576228548</v>
+        <v>-0.1088191576228549</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9340388224774749</v>
+        <v>-0.9340388224774662</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9241303851581092</v>
+        <v>-0.9241303851581086</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9308070941393508</v>
+        <v>-0.9308070941393475</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9336757003037862</v>
+        <v>-0.9336757003037863</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9210730213965773</v>
+        <v>-0.9210730213965758</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9239861244558457</v>
+        <v>-0.9239861244558446</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.922538138892669</v>
+        <v>-0.9225381388926691</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9316243441729496</v>
+        <v>-0.9316243441729442</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9293366934538567</v>
+        <v>-0.9293366934538543</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9298974519221364</v>
+        <v>-0.9298974519221292</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9361492809956677</v>
+        <v>-0.9361492809956661</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9285414369774225</v>
+        <v>-0.9285414369774221</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9280192395607388</v>
+        <v>-0.9280192395607373</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9232977123994773</v>
+        <v>-0.9232977123994672</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9351650303511998</v>
+        <v>-0.9351650303511895</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9126223685356055</v>
+        <v>-0.912622368535601</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9342383049072499</v>
+        <v>-0.9342383049072481</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9232998229136289</v>
+        <v>-0.9232998229136228</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9104999340135254</v>
+        <v>-0.9104999340135252</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08903470240028805</v>
+        <v>-0.08903470240027556</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1762003551399419</v>
+        <v>-0.1762003551399357</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07098550144421861</v>
+        <v>-0.07098550144420215</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.166772883815999</v>
+        <v>-0.166772883815993</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1642606641665413</v>
+        <v>-0.1642606641665392</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08391528538802377</v>
+        <v>0.08391528538803307</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.05265823137438855</v>
+        <v>-0.05265823137437659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1489249295230312</v>
+        <v>-0.1489249295230159</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03028920361928725</v>
+        <v>-0.03028920361928618</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.09406159296473557</v>
+        <v>-0.09406159296472456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03218835556776517</v>
+        <v>0.03218835556777764</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1192819858449536</v>
+        <v>0.1192819858449607</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06516866038864098</v>
+        <v>-0.06516866038863217</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09887238544758199</v>
+        <v>-0.09887238544756977</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.06087473191433346</v>
+        <v>-0.06087473191432508</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1288289646644652</v>
+        <v>-0.1288289646644548</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1841036115038203</v>
+        <v>-0.1841036115038105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.05782814151105366</v>
+        <v>-0.05782814151104419</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1351114441673089</v>
+        <v>-0.1351114441672966</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01211891399513403</v>
+        <v>0.01211891399514699</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2260652012745395</v>
+        <v>-0.2260652012745407</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03291552608447957</v>
+        <v>0.03291552608449487</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01362265389273965</v>
+        <v>-0.01362265389272819</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.03754127112953612</v>
+        <v>-0.03754127112952226</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.105580634109818</v>
+        <v>-0.1055806341098043</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.01987405332422178</v>
+        <v>-0.01987405332420824</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1064780912146807</v>
+        <v>0.1064780912146852</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1953102332719954</v>
+        <v>-0.1953102332719787</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.192226556279149</v>
+        <v>-0.192226556279144</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1952692817051762</v>
+        <v>-0.1952692817051651</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.196010328993974</v>
+        <v>-0.1960103289939707</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1905843510301294</v>
+        <v>-0.1905843510301176</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.205574589337933</v>
+        <v>-0.2055745893379204</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1906343100137179</v>
+        <v>-0.1906343100137134</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1944301842822293</v>
+        <v>-0.1944301842822196</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1935963624580692</v>
+        <v>-0.1935963624580675</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1938007523350001</v>
+        <v>-0.1938007523349937</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1960794706196206</v>
+        <v>-0.1960794706196067</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1933065008107812</v>
+        <v>-0.1933065008107675</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2842671493177182</v>
+        <v>-0.2842671493177169</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1913952247770472</v>
+        <v>-0.191395224777036</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1957207228173644</v>
+        <v>-0.1957207228173486</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1875041872948797</v>
+        <v>-0.187504187294878</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1953829422752036</v>
+        <v>-0.1953829422751901</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1913959940346698</v>
+        <v>-0.1913959940346603</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1857251379687618</v>
+        <v>-0.1857251379687547</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8015673060552717</v>
+        <v>-0.8015673060552647</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8887329587949278</v>
+        <v>-0.8887329587949276</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7835181050992015</v>
+        <v>-0.783518105099193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8793054874709845</v>
+        <v>-0.8793054874709814</v>
       </c>
       <c r="F6" t="n">
         <v>-0.8767932678215277</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6655543874543388</v>
+        <v>-0.6655543874543325</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7651908350293716</v>
+        <v>-0.7651908350293651</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8614575331780153</v>
+        <v>-0.8614575331780091</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7646980353421259</v>
+        <v>-0.7646980353421206</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8065941966197183</v>
+        <v>-0.8065941966197131</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6803442480872164</v>
+        <v>-0.6803442480872107</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5932506178100317</v>
+        <v>-0.5932506178100316</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7777012640436263</v>
+        <v>-0.7777012640436196</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.848342058289943</v>
+        <v>-0.8483420582899358</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8103444047566954</v>
+        <v>-0.8103444047566928</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.841361568319452</v>
+        <v>-0.8413615683194451</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.8966362151588045</v>
+        <v>-0.8966362151587967</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7703607451660381</v>
+        <v>-0.7703607451660319</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8476440478222935</v>
+        <v>-0.8476440478222872</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7373507588472273</v>
+        <v>-0.7373507588472203</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8830146485610644</v>
+        <v>-0.8830146485610652</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7165541467578812</v>
+        <v>-0.7165541467578709</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7630923267351024</v>
+        <v>-0.763092326735095</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.7500738747845188</v>
+        <v>-0.7500738747845125</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8181132377648007</v>
+        <v>-0.8181132377647939</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.7324066569792053</v>
+        <v>-0.7324066569791983</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.6060545124403052</v>
+        <v>-0.6060545124403047</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9078428369269783</v>
+        <v>-0.9078428369269699</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9047591599341355</v>
+        <v>-0.9047591599341347</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9078018853601598</v>
+        <v>-0.9078018853601566</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9085429326489578</v>
+        <v>-0.9085429326489577</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9400540238724916</v>
+        <v>-0.9400540238724837</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9399834210607703</v>
+        <v>-0.9399834210607672</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9031669136687024</v>
+        <v>-0.9031669136687023</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9069627879372132</v>
+        <v>-0.9069627879372085</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9430660353004334</v>
+        <v>-0.9430660353004333</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.943270425177363</v>
+        <v>-0.9432704251773606</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9086120742746038</v>
+        <v>-0.9086120742745966</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9427761736531459</v>
+        <v>-0.9427761736531378</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9412165966042413</v>
+        <v>-0.9412165966042423</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9408648976194074</v>
+        <v>-0.9408648976193997</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9451903956597272</v>
+        <v>-0.9451903956597166</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.9000367909498651</v>
+        <v>-0.9000367909498656</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.9079155459301897</v>
+        <v>-0.9079155459301819</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9039285976896551</v>
+        <v>-0.9039285976896485</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8982577416237454</v>
+        <v>-0.8982577416237453</v>
       </c>
     </row>
   </sheetData>
@@ -6748,49 +6748,49 @@
         <v>-0.9954295121106933</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8901281043905194</v>
+        <v>-0.8901281043905191</v>
       </c>
       <c r="E2" t="n">
         <v>-1.010649604737214</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.215978715021598</v>
+        <v>-1.215978715021597</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3016806673118441</v>
+        <v>-0.301680667311844</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.685583696758349</v>
+        <v>-0.6855836967583488</v>
       </c>
       <c r="I2" t="n">
         <v>-1.012474387517319</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.738199003464853</v>
+        <v>-0.7381990034648536</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9479987471681008</v>
+        <v>-0.9479987471681004</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.303522739637468</v>
+        <v>-1.303522739637467</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9513546587489088</v>
+        <v>-0.951354658748909</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9239133671757785</v>
+        <v>-0.9239133671757781</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.040748395694001</v>
+        <v>-1.040748395694</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8113628438194508</v>
+        <v>-0.8113628438194505</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9570531766070285</v>
+        <v>-0.9570531766070282</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.497948398655155</v>
+        <v>-1.497948398655154</v>
       </c>
       <c r="S2" t="n">
         <v>-1.160324158343884</v>
@@ -6799,28 +6799,28 @@
         <v>-1.122115788944807</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8469753791152747</v>
+        <v>-0.8469753791152742</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8361209669994301</v>
+        <v>-0.8361209669994297</v>
       </c>
       <c r="W2" t="n">
         <v>-0.5263139307247611</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3335511372799065</v>
+        <v>-0.333551137279906</v>
       </c>
       <c r="Y2" t="n">
         <v>-0.1516533003862296</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.8589717932238681</v>
+        <v>-0.8589717932238679</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.6982804747331439</v>
+        <v>-0.698280474733144</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.4524704766848968</v>
+        <v>-0.4524704766848969</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9416363935550823</v>
+        <v>-0.9416363935550819</v>
       </c>
       <c r="C3" t="n">
         <v>-0.933508011915068</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="E3" t="n">
         <v>-0.9388231367776955</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9420035616020829</v>
+        <v>-0.9420035616020831</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9313943725526878</v>
+        <v>-0.9313943725526876</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="J3" t="n">
         <v>-0.9335725761196929</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="M3" t="n">
         <v>-0.9339661831941337</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9397291348088616</v>
+        <v>-0.9397291348088613</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9379220604460039</v>
+        <v>-0.9379220604460037</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9383650180372549</v>
+        <v>-0.9383650180372546</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9433034992235385</v>
+        <v>-0.9433034992235378</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9373289384765178</v>
+        <v>-0.9373289384765177</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9364522029775608</v>
+        <v>-0.9364522029775607</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9331517134064535</v>
+        <v>-0.933151713406453</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9425260142280416</v>
+        <v>-0.9425260142280414</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9247789810847679</v>
+        <v>-0.9247789810847676</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.9417939698765152</v>
+        <v>-0.9417939698765149</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.933153380558907</v>
+        <v>-0.9331533805589068</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.9230095215171669</v>
+        <v>-0.9230095215171671</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.23903697697627</v>
+        <v>-0.2390369769762698</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2381554217590074</v>
+        <v>-0.2381554217590079</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1995489227654301</v>
+        <v>-0.1995489227654298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2442102136351133</v>
+        <v>-0.2442102136351135</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3193908468790702</v>
+        <v>-0.3193908468790706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01493325815107537</v>
+        <v>0.01493325815107557</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1249948880652054</v>
+        <v>-0.1249948880652044</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2441427063025583</v>
+        <v>-0.2441427063025578</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1567893877050308</v>
+        <v>-0.1567893877050302</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2206420925064617</v>
+        <v>-0.2206420925064614</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3502264129880519</v>
+        <v>-0.350226412988051</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2223818284896694</v>
+        <v>-0.2223818284896698</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2118632543240714</v>
+        <v>-0.2118632543240708</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2544482502727903</v>
+        <v>-0.2544482502727901</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1708399101956601</v>
+        <v>-0.1708399101956595</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2239423257144716</v>
+        <v>-0.2239423257144709</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4210922826386422</v>
+        <v>-0.4210922826386418</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2980322116291784</v>
+        <v>-0.2980322116291779</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2841057096485413</v>
+        <v>-0.2841057096485402</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1838202611274858</v>
+        <v>-0.1838202611274848</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2628612172038228</v>
+        <v>-0.2628612172038242</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.06694292858597921</v>
+        <v>-0.06694292858597853</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003316846089669116</v>
+        <v>0.003316846089669524</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06961647168517469</v>
+        <v>0.0696164716851749</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1881928132010621</v>
+        <v>-0.1881928132010617</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.129622714543923</v>
+        <v>-0.1296227145439227</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.03921272224818052</v>
+        <v>-0.03921272224818059</v>
       </c>
     </row>
     <row r="5">
@@ -7006,73 +7006,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2183230893250441</v>
+        <v>-0.2183230893250447</v>
       </c>
       <c r="C5" t="n">
         <v>-0.2155857620566689</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2180303094928385</v>
+        <v>-0.2180303094928382</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.219530120636336</v>
+        <v>-0.2195301206363358</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2145899929375535</v>
+        <v>-0.2145899929375546</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2280007607454015</v>
+        <v>-0.2280007607454008</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2160439333357443</v>
+        <v>-0.2160439333357447</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2176279159082104</v>
+        <v>-0.2176279159082103</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2169692585226854</v>
+        <v>-0.2169692585226852</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2171307113632279</v>
+        <v>-0.217130711363227</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2189307297650547</v>
+        <v>-0.2189307297650541</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2167530725296001</v>
+        <v>-0.2167530725295999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2994307745689981</v>
+        <v>-0.2994307745689995</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2152305230430138</v>
+        <v>-0.2152305230430129</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2186473456138862</v>
+        <v>-0.218647345613886</v>
       </c>
       <c r="Y5" t="n">
         <v>-0.2121787604293463</v>
@@ -7081,10 +7081,10 @@
         <v>-0.2183805240438516</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2152311307005068</v>
+        <v>-0.2152311307005066</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2107186787411158</v>
+        <v>-0.2107186787411154</v>
       </c>
     </row>
     <row r="6">
@@ -7094,25 +7094,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9340069162742088</v>
+        <v>-0.9340069162742084</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9331253610569453</v>
+        <v>-0.9331253610569454</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8945188620633684</v>
+        <v>-0.8945188620633682</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9391801529330515</v>
+        <v>-0.9391801529330516</v>
       </c>
       <c r="F6" t="n">
         <v>-1.014360786177009</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7168647053389063</v>
+        <v>-0.7168647053389059</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8199648273631424</v>
+        <v>-0.8199648273631422</v>
       </c>
       <c r="I6" t="n">
         <v>-0.9391126456004965</v>
@@ -7121,58 +7121,58 @@
         <v>-0.8746724957706355</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9156120318044</v>
+        <v>-0.9156120318043998</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.04519635228599</v>
+        <v>-1.045196352285989</v>
       </c>
       <c r="M6" t="n">
         <v>-0.91735176778761</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9068331936220096</v>
+        <v>-0.9068331936220092</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9862462137627732</v>
+        <v>-0.9862462137627728</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.902637873685643</v>
+        <v>-0.9026378736856426</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.918912265012411</v>
+        <v>-0.9189122650124106</v>
       </c>
       <c r="R6" t="n">
         <v>-1.116062221936581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9930021509271162</v>
+        <v>-0.993002150927116</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9790756489464785</v>
+        <v>-0.9790756489464778</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9156182246174682</v>
+        <v>-0.9156182246174676</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9097632755335883</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7987408920759597</v>
+        <v>-0.7987408920759591</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7284811174003114</v>
+        <v>-0.7284811174003112</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.6253534676127642</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8831627524990008</v>
+        <v>-0.8831627524990007</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.8245926538418609</v>
+        <v>-0.8245926538418606</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.7341826615461197</v>
+        <v>-0.7341826615461198</v>
       </c>
     </row>
     <row r="7">
@@ -7188,7 +7188,7 @@
         <v>-0.9105557013546057</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9130002487907763</v>
@@ -7197,70 +7197,70 @@
         <v>-0.9145000599342759</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9463879564275356</v>
+        <v>-0.9463879564275353</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9458838688110057</v>
+        <v>-0.9458838688110055</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="M7" t="n">
         <v>-0.9110138726336831</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.912597855206148</v>
+        <v>-0.9125978552061483</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9487672220126681</v>
+        <v>-0.9487672220126678</v>
       </c>
       <c r="P7" t="n">
         <v>-0.9489286748532082</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9139006690629919</v>
+        <v>-0.9139006690629918</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9485510360195802</v>
+        <v>-0.9485510360195801</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9463328328987618</v>
+        <v>-0.9463328328987617</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9470284865329949</v>
+        <v>-0.9470284865329947</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9504453091038662</v>
+        <v>-0.9504453091038658</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.9071486997272845</v>
+        <v>-0.9071486997272846</v>
       </c>
       <c r="Z7" t="n">
         <v>-0.9133504633417906</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9102010699984446</v>
+        <v>-0.9102010699984447</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.9056886180390546</v>
+        <v>-0.9056886180390548</v>
       </c>
     </row>
   </sheetData>
